--- a/files/Cases/RQ1_SPLSummary_medians.xlsx
+++ b/files/Cases/RQ1_SPLSummary_medians.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EFG_L2" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EFG_L3" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EFG_L4" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ESG-Fx_L2" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ESG-Fx_L3" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ESG-Fx_L4" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RandomWalk_L0" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="ESG-Fx_L2" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ESG-Fx_L3" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ESG-Fx_L4" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="EFG_L2" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="EFG_L3" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="EFG_L4" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="RandomWalk_L0" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,16 +23,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -43,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -51,21 +48,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -431,118 +419,148 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V9"/>
+  <dimension ref="A1:W9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="27" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="23" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
+    <col width="25" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="31" customWidth="1" min="19" max="19"/>
+    <col width="17" customWidth="1" min="20" max="20"/>
+    <col width="30" customWidth="1" min="21" max="21"/>
+    <col width="19" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="23" max="23"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>SPL Name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Approach</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Coverage Type</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Total Elapsed Time(ms)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Total TestGenTime(ms)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Total Parse Time (ms)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Total TestGenPeakMemory(MB)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Total NumberOfEFGVertices</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Total NumberOfEFGEdges</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Total NumberOfEFGTestCases</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Total NumberOfEFGTestEvents</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Event Coverage(%)</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Event Coverage Analysis Time(ms)</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Edge Coverage(%)</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Edge Coverage Analysis Time(ms)</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Total TestExecTime(ms)</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Total TestExecPeakMemory(MB)</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Total ESGFx_Vertices</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Total ESGFx_Edges</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Total ESGFxModelLoadTimeMs</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Processed Products</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Failed Products</t>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>TotalElapsedTime(ms)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>TotalTestGenTime(ms)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>AlgTestGenTime(ms)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ESGFxModelLoadTime(ms)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>TestCaseRecordingTime(ms)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>TransformationTime(ms)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>TransformationShare(%)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>TestGenPeakMemory(MB)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>TestExecTime(ms)</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>TestExecPeakMemory(MB)</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>NumberOfESGFxVertices</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>NumberOfESGFxEdges</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>NumberOfESGFxTestCases</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>NumberOfESGFxTestEvents</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>EventCoverage(%)</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>EventCoverageAnalysisTime(ms)</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>EdgeCoverage(%)</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>EdgeCoverageAnalysisTime(ms)</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>ProcessedProducts</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>FailedProducts</t>
         </is>
       </c>
     </row>
@@ -554,7 +572,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>EFG</t>
+          <t>ESG-Fx</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -563,60 +581,63 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>701477.47</v>
+        <v>26267.36</v>
       </c>
       <c r="E2" t="n">
-        <v>664279.5900000001</v>
+        <v>21286.39</v>
       </c>
       <c r="F2" t="n">
-        <v>29944.23</v>
+        <v>15850</v>
       </c>
       <c r="G2" t="n">
-        <v>10</v>
+        <v>2873.1</v>
       </c>
       <c r="H2" t="n">
-        <v>11664</v>
+        <v>2563.29</v>
       </c>
       <c r="I2" t="n">
-        <v>9939</v>
+        <v>2117.71</v>
       </c>
       <c r="J2" t="n">
-        <v>9507</v>
+        <v>13.36094637223975</v>
       </c>
       <c r="K2" t="n">
-        <v>29892</v>
+        <v>11</v>
       </c>
       <c r="L2" t="n">
-        <v>98.34198795180724</v>
+        <v>128.77</v>
       </c>
       <c r="M2" t="n">
-        <v>2093.96</v>
+        <v>2.7</v>
       </c>
       <c r="N2" t="n">
-        <v>96.40536144578313</v>
+        <v>12660</v>
       </c>
       <c r="O2" t="n">
-        <v>3267.84</v>
+        <v>16395</v>
       </c>
       <c r="P2" t="n">
-        <v>242.08</v>
+        <v>4407</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.6</v>
+        <v>16506</v>
       </c>
       <c r="R2" t="n">
-        <v>12660</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>16395</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>3516.51</v>
+        <v>100</v>
       </c>
       <c r="U2" t="n">
+        <v>2793.43</v>
+      </c>
+      <c r="V2" t="n">
         <v>498</v>
       </c>
-      <c r="V2" t="n">
+      <c r="W2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -628,7 +649,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>EFG</t>
+          <t>ESG-Fx</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -637,60 +658,63 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>44353.24</v>
+        <v>7183.879999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>40288.09</v>
+        <v>5786.289999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>2907.59</v>
+        <v>4613.86</v>
       </c>
       <c r="G3" t="n">
-        <v>9</v>
+        <v>367.15</v>
       </c>
       <c r="H3" t="n">
-        <v>470</v>
+        <v>805.28</v>
       </c>
       <c r="I3" t="n">
-        <v>1144</v>
+        <v>560.5999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>1120</v>
+        <v>12.15034699795832</v>
       </c>
       <c r="K3" t="n">
-        <v>3178</v>
+        <v>11</v>
       </c>
       <c r="L3" t="n">
+        <v>33.96</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="N3" t="n">
+        <v>554</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1566</v>
+      </c>
+      <c r="P3" t="n">
+        <v>651</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1994</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
         <v>100</v>
       </c>
-      <c r="M3" t="n">
-        <v>476.65</v>
-      </c>
-      <c r="N3" t="n">
-        <v>98.1054761904762</v>
-      </c>
-      <c r="O3" t="n">
-        <v>872.0200000000001</v>
-      </c>
-      <c r="P3" t="n">
-        <v>44.75</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="R3" t="n">
-        <v>554</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1566</v>
-      </c>
-      <c r="T3" t="n">
-        <v>456.04</v>
-      </c>
       <c r="U3" t="n">
+        <v>703.45</v>
+      </c>
+      <c r="V3" t="n">
         <v>42</v>
       </c>
-      <c r="V3" t="n">
+      <c r="W3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -702,7 +726,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EFG</t>
+          <t>ESG-Fx</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -711,60 +735,63 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>749836.8500000001</v>
+        <v>42054.7</v>
       </c>
       <c r="E4" t="n">
-        <v>684224.61</v>
+        <v>32479.04</v>
       </c>
       <c r="F4" t="n">
-        <v>54302.03999999999</v>
+        <v>24746.52</v>
       </c>
       <c r="G4" t="n">
-        <v>17</v>
+        <v>3616.42</v>
       </c>
       <c r="H4" t="n">
-        <v>24985</v>
+        <v>4116.1</v>
       </c>
       <c r="I4" t="n">
-        <v>28895</v>
+        <v>2836.42</v>
       </c>
       <c r="J4" t="n">
-        <v>10931</v>
+        <v>11.46189444010713</v>
       </c>
       <c r="K4" t="n">
-        <v>122939</v>
+        <v>15</v>
       </c>
       <c r="L4" t="n">
-        <v>35.43786057692308</v>
+        <v>310.83</v>
       </c>
       <c r="M4" t="n">
-        <v>3283.37</v>
+        <v>3.12</v>
       </c>
       <c r="N4" t="n">
-        <v>37.40694711538462</v>
+        <v>25817</v>
       </c>
       <c r="O4" t="n">
-        <v>6418.12</v>
+        <v>29727</v>
       </c>
       <c r="P4" t="n">
-        <v>344.66</v>
+        <v>2949</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.94</v>
+        <v>149487</v>
       </c>
       <c r="R4" t="n">
-        <v>25817</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>29727</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>5065</v>
+        <v>100</v>
       </c>
       <c r="U4" t="n">
+        <v>6212.360000000001</v>
+      </c>
+      <c r="V4" t="n">
         <v>416</v>
       </c>
-      <c r="V4" t="n">
+      <c r="W4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -776,7 +803,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>EFG</t>
+          <t>ESG-Fx</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -785,60 +812,63 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12632.47</v>
+        <v>1633.2</v>
       </c>
       <c r="E5" t="n">
-        <v>11998.43</v>
+        <v>1334.05</v>
       </c>
       <c r="F5" t="n">
-        <v>487.32</v>
+        <v>957.2299999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>8</v>
+        <v>43.56999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>86</v>
+        <v>333.25</v>
       </c>
       <c r="I5" t="n">
-        <v>78</v>
+        <v>150.82</v>
       </c>
       <c r="J5" t="n">
-        <v>78</v>
+        <v>15.75587894236495</v>
       </c>
       <c r="K5" t="n">
-        <v>294</v>
+        <v>9</v>
       </c>
       <c r="L5" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="N5" t="n">
+        <v>110</v>
+      </c>
+      <c r="O5" t="n">
+        <v>108</v>
+      </c>
+      <c r="P5" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>109</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
         <v>100</v>
       </c>
-      <c r="M5" t="n">
-        <v>78.44999999999999</v>
-      </c>
-      <c r="N5" t="n">
-        <v>100</v>
-      </c>
-      <c r="O5" t="n">
-        <v>90.59</v>
-      </c>
-      <c r="P5" t="n">
-        <v>11.06</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>110</v>
-      </c>
-      <c r="S5" t="n">
-        <v>108</v>
-      </c>
-      <c r="T5" t="n">
-        <v>75.12</v>
-      </c>
       <c r="U5" t="n">
+        <v>68.05</v>
+      </c>
+      <c r="V5" t="n">
         <v>12</v>
       </c>
-      <c r="V5" t="n">
+      <c r="W5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -850,7 +880,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>EFG</t>
+          <t>ESG-Fx</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -859,60 +889,63 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3426157.82</v>
+        <v>99029.62</v>
       </c>
       <c r="E6" t="n">
-        <v>3303437.810000001</v>
+        <v>79572.64</v>
       </c>
       <c r="F6" t="n">
-        <v>102641.76</v>
+        <v>59598.64</v>
       </c>
       <c r="G6" t="n">
+        <v>10789.87</v>
+      </c>
+      <c r="H6" t="n">
+        <v>9184.129999999999</v>
+      </c>
+      <c r="I6" t="n">
+        <v>5528.9</v>
+      </c>
+      <c r="J6" t="n">
+        <v>9.27688953976131</v>
+      </c>
+      <c r="K6" t="n">
         <v>15</v>
       </c>
-      <c r="H6" t="n">
-        <v>82522</v>
-      </c>
-      <c r="I6" t="n">
-        <v>108882</v>
-      </c>
-      <c r="J6" t="n">
-        <v>83870</v>
-      </c>
-      <c r="K6" t="n">
-        <v>353670</v>
-      </c>
       <c r="L6" t="n">
-        <v>93.18321321321322</v>
+        <v>648.1800000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>5843.58</v>
+        <v>3.07</v>
       </c>
       <c r="N6" t="n">
-        <v>68.80961336336337</v>
+        <v>87850</v>
       </c>
       <c r="O6" t="n">
-        <v>10806.84</v>
+        <v>149694</v>
       </c>
       <c r="P6" t="n">
-        <v>759.6399999999999</v>
+        <v>38236</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.9</v>
+        <v>244862</v>
       </c>
       <c r="R6" t="n">
-        <v>87850</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>149694</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>8671.389999999999</v>
+        <v>100</v>
       </c>
       <c r="U6" t="n">
+        <v>13234.34</v>
+      </c>
+      <c r="V6" t="n">
         <v>2664</v>
       </c>
-      <c r="V6" t="n">
+      <c r="W6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -924,7 +957,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>EFG</t>
+          <t>ESG-Fx</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -933,60 +966,63 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>629489.51</v>
+        <v>33732.66</v>
       </c>
       <c r="E7" t="n">
-        <v>579951.01</v>
+        <v>25692.00999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>38695.74000000001</v>
+        <v>19662.1</v>
       </c>
       <c r="G7" t="n">
-        <v>13.31</v>
+        <v>2420.1</v>
       </c>
       <c r="H7" t="n">
-        <v>11760</v>
+        <v>3609.809999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>14970</v>
+        <v>2091.02</v>
       </c>
       <c r="J7" t="n">
-        <v>14390</v>
+        <v>10.63477451543833</v>
       </c>
       <c r="K7" t="n">
-        <v>186754</v>
+        <v>13</v>
       </c>
       <c r="L7" t="n">
-        <v>92.25575000000001</v>
+        <v>256.25</v>
       </c>
       <c r="M7" t="n">
-        <v>7454.22</v>
+        <v>2.82</v>
       </c>
       <c r="N7" t="n">
-        <v>92.56637500000001</v>
+        <v>12560</v>
       </c>
       <c r="O7" t="n">
-        <v>8215.790000000001</v>
+        <v>15770</v>
       </c>
       <c r="P7" t="n">
-        <v>434.49</v>
+        <v>2910</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.67</v>
+        <v>77553</v>
       </c>
       <c r="R7" t="n">
-        <v>12560</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>15770</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3221.92</v>
+        <v>100</v>
       </c>
       <c r="U7" t="n">
+        <v>5885.52</v>
+      </c>
+      <c r="V7" t="n">
         <v>400</v>
       </c>
-      <c r="V7" t="n">
+      <c r="W7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -998,7 +1034,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>EFG</t>
+          <t>ESG-Fx</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1007,60 +1043,63 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>22844.7</v>
+        <v>3396.57</v>
       </c>
       <c r="E8" t="n">
-        <v>21542.64</v>
+        <v>2785.09</v>
       </c>
       <c r="F8" t="n">
-        <v>842.05</v>
+        <v>2205.55</v>
       </c>
       <c r="G8" t="n">
-        <v>8</v>
+        <v>167.93</v>
       </c>
       <c r="H8" t="n">
-        <v>269</v>
+        <v>411.61</v>
       </c>
       <c r="I8" t="n">
-        <v>366</v>
+        <v>303.54</v>
       </c>
       <c r="J8" t="n">
-        <v>156</v>
+        <v>13.76255355806942</v>
       </c>
       <c r="K8" t="n">
-        <v>348</v>
+        <v>10</v>
       </c>
       <c r="L8" t="n">
-        <v>80.05173913043478</v>
+        <v>19.33</v>
       </c>
       <c r="M8" t="n">
-        <v>115.14</v>
+        <v>2.29</v>
       </c>
       <c r="N8" t="n">
-        <v>35.75304347826086</v>
+        <v>315</v>
       </c>
       <c r="O8" t="n">
-        <v>227.54</v>
+        <v>587</v>
       </c>
       <c r="P8" t="n">
-        <v>18.16</v>
+        <v>138</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.11</v>
+        <v>634</v>
       </c>
       <c r="R8" t="n">
-        <v>315</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>587</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>190.4</v>
+        <v>100</v>
       </c>
       <c r="U8" t="n">
+        <v>289.45</v>
+      </c>
+      <c r="V8" t="n">
         <v>23</v>
       </c>
-      <c r="V8" t="n">
+      <c r="W8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1072,7 +1111,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>EFG</t>
+          <t>ESG-Fx</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1081,60 +1120,63 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1207824.08</v>
+        <v>713062.16</v>
       </c>
       <c r="E9" t="n">
-        <v>809451.26</v>
+        <v>645804.66</v>
       </c>
       <c r="F9" t="n">
-        <v>377991.71</v>
+        <v>611119.5600000001</v>
       </c>
       <c r="G9" t="n">
-        <v>40.67</v>
+        <v>14492.28</v>
       </c>
       <c r="H9" t="n">
-        <v>72550</v>
+        <v>20192.82</v>
       </c>
       <c r="I9" t="n">
-        <v>195587</v>
+        <v>7342.95</v>
       </c>
       <c r="J9" t="n">
-        <v>8293</v>
+        <v>1.201557024291613</v>
       </c>
       <c r="K9" t="n">
-        <v>28756</v>
+        <v>127.66</v>
       </c>
       <c r="L9" t="n">
-        <v>8.482624999999999</v>
+        <v>1064.01</v>
       </c>
       <c r="M9" t="n">
-        <v>2590.47</v>
+        <v>4.67</v>
       </c>
       <c r="N9" t="n">
-        <v>4.095125</v>
+        <v>73350</v>
       </c>
       <c r="O9" t="n">
-        <v>11191.51</v>
+        <v>210644</v>
       </c>
       <c r="P9" t="n">
-        <v>193</v>
+        <v>118564</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.06</v>
+        <v>1137997</v>
       </c>
       <c r="R9" t="n">
-        <v>73350</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>210644</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>10802.15</v>
+        <v>100</v>
       </c>
       <c r="U9" t="n">
+        <v>59027.81</v>
+      </c>
+      <c r="V9" t="n">
         <v>400</v>
       </c>
-      <c r="V9" t="n">
+      <c r="W9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1149,118 +1191,148 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V9"/>
+  <dimension ref="A1:W9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="27" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="23" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
+    <col width="25" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="31" customWidth="1" min="19" max="19"/>
+    <col width="17" customWidth="1" min="20" max="20"/>
+    <col width="30" customWidth="1" min="21" max="21"/>
+    <col width="19" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="23" max="23"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>SPL Name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Approach</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Coverage Type</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Total Elapsed Time(ms)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Total TestGenTime(ms)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Total Parse Time (ms)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Total TestGenPeakMemory(MB)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Total NumberOfEFGVertices</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Total NumberOfEFGEdges</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Total NumberOfEFGTestCases</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Total NumberOfEFGTestEvents</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Event Coverage(%)</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Event Coverage Analysis Time(ms)</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Edge Coverage(%)</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Edge Coverage Analysis Time(ms)</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Total TestExecTime(ms)</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Total TestExecPeakMemory(MB)</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Total ESGFx_Vertices</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Total ESGFx_Edges</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Total ESGFxModelLoadTimeMs</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Processed Products</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Failed Products</t>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>TotalElapsedTime(ms)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>TotalTestGenTime(ms)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>AlgTestGenTime(ms)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ESGFxModelLoadTime(ms)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>TestCaseRecordingTime(ms)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>TransformationTime(ms)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>TransformationShare(%)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>TestGenPeakMemory(MB)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>TestExecTime(ms)</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>TestExecPeakMemory(MB)</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>NumberOfESGFxVertices</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>NumberOfESGFxEdges</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>NumberOfESGFxTestCases</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>NumberOfESGFxTestEvents</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>EventCoverage(%)</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>EventCoverageAnalysisTime(ms)</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>EdgeCoverage(%)</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>EdgeCoverageAnalysisTime(ms)</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>ProcessedProducts</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>FailedProducts</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1344,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>EFG</t>
+          <t>ESG-Fx</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1281,60 +1353,63 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>701119.02</v>
+        <v>36947.39999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>662942.1599999999</v>
+        <v>27422.8</v>
       </c>
       <c r="F2" t="n">
-        <v>31777.74</v>
+        <v>21625.19</v>
       </c>
       <c r="G2" t="n">
-        <v>10</v>
+        <v>3003.81</v>
       </c>
       <c r="H2" t="n">
-        <v>11664</v>
+        <v>2793.8</v>
       </c>
       <c r="I2" t="n">
-        <v>9939</v>
+        <v>5977.91</v>
       </c>
       <c r="J2" t="n">
-        <v>7485</v>
+        <v>27.64327157356767</v>
       </c>
       <c r="K2" t="n">
-        <v>26640</v>
+        <v>11</v>
       </c>
       <c r="L2" t="n">
-        <v>99.44692771084335</v>
+        <v>124.86</v>
       </c>
       <c r="M2" t="n">
-        <v>1986.23</v>
+        <v>2.72</v>
       </c>
       <c r="N2" t="n">
-        <v>97.60373493975904</v>
+        <v>12660</v>
       </c>
       <c r="O2" t="n">
-        <v>3076.07</v>
+        <v>16395</v>
       </c>
       <c r="P2" t="n">
-        <v>223.03</v>
+        <v>4983</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.59</v>
+        <v>14043</v>
       </c>
       <c r="R2" t="n">
-        <v>12660</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>16395</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>3342.26</v>
+        <v>100</v>
       </c>
       <c r="U2" t="n">
+        <v>3419.54</v>
+      </c>
+      <c r="V2" t="n">
         <v>498</v>
       </c>
-      <c r="V2" t="n">
+      <c r="W2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1346,7 +1421,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>EFG</t>
+          <t>ESG-Fx</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1355,60 +1430,63 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>48608.57</v>
+        <v>15667.65</v>
       </c>
       <c r="E3" t="n">
-        <v>41895.55</v>
+        <v>11698.18</v>
       </c>
       <c r="F3" t="n">
-        <v>4725.77</v>
+        <v>10143.67</v>
       </c>
       <c r="G3" t="n">
-        <v>11</v>
+        <v>466.62</v>
       </c>
       <c r="H3" t="n">
-        <v>470</v>
+        <v>1087.89</v>
       </c>
       <c r="I3" t="n">
-        <v>1144</v>
+        <v>1851.1</v>
       </c>
       <c r="J3" t="n">
-        <v>2184</v>
+        <v>18.24881921434747</v>
       </c>
       <c r="K3" t="n">
-        <v>7346</v>
+        <v>16</v>
       </c>
       <c r="L3" t="n">
+        <v>36.78</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N3" t="n">
+        <v>554</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1566</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2063</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>4444</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
         <v>100</v>
       </c>
-      <c r="M3" t="n">
-        <v>998.08</v>
-      </c>
-      <c r="N3" t="n">
-        <v>100</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1307.45</v>
-      </c>
-      <c r="P3" t="n">
-        <v>62.2</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="R3" t="n">
-        <v>554</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1566</v>
-      </c>
-      <c r="T3" t="n">
-        <v>426.45</v>
-      </c>
       <c r="U3" t="n">
+        <v>1852.23</v>
+      </c>
+      <c r="V3" t="n">
         <v>42</v>
       </c>
-      <c r="V3" t="n">
+      <c r="W3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1420,7 +1498,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EFG</t>
+          <t>ESG-Fx</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1429,60 +1507,63 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>770353.0900000001</v>
+        <v>73187.89</v>
       </c>
       <c r="E4" t="n">
-        <v>695590.7399999999</v>
+        <v>49218.44</v>
       </c>
       <c r="F4" t="n">
-        <v>62171.34000000001</v>
+        <v>39202.21</v>
       </c>
       <c r="G4" t="n">
+        <v>3853.98</v>
+      </c>
+      <c r="H4" t="n">
+        <v>6162.25</v>
+      </c>
+      <c r="I4" t="n">
+        <v>11460.6</v>
+      </c>
+      <c r="J4" t="n">
+        <v>29.23457631597811</v>
+      </c>
+      <c r="K4" t="n">
         <v>17</v>
       </c>
-      <c r="H4" t="n">
-        <v>24985</v>
-      </c>
-      <c r="I4" t="n">
-        <v>28895</v>
-      </c>
-      <c r="J4" t="n">
-        <v>14938</v>
-      </c>
-      <c r="K4" t="n">
-        <v>182634</v>
-      </c>
       <c r="L4" t="n">
-        <v>37.22170673076923</v>
+        <v>207.77</v>
       </c>
       <c r="M4" t="n">
-        <v>4501.78</v>
+        <v>3.19</v>
       </c>
       <c r="N4" t="n">
-        <v>38.85050480769231</v>
+        <v>25817</v>
       </c>
       <c r="O4" t="n">
-        <v>7778.48</v>
+        <v>29727</v>
       </c>
       <c r="P4" t="n">
-        <v>435.29</v>
+        <v>4240</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.95</v>
+        <v>205668</v>
       </c>
       <c r="R4" t="n">
-        <v>25817</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>29727</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>4849.84</v>
+        <v>100</v>
       </c>
       <c r="U4" t="n">
+        <v>12436.78</v>
+      </c>
+      <c r="V4" t="n">
         <v>416</v>
       </c>
-      <c r="V4" t="n">
+      <c r="W4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1494,7 +1575,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>EFG</t>
+          <t>ESG-Fx</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1503,60 +1584,63 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13007.22</v>
+        <v>1859.99</v>
       </c>
       <c r="E5" t="n">
-        <v>12223.56</v>
+        <v>1560.49</v>
       </c>
       <c r="F5" t="n">
-        <v>571.9300000000001</v>
+        <v>1142.34</v>
       </c>
       <c r="G5" t="n">
-        <v>8</v>
+        <v>55.26000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>86</v>
+        <v>362.89</v>
       </c>
       <c r="I5" t="n">
-        <v>78</v>
+        <v>243.87</v>
       </c>
       <c r="J5" t="n">
-        <v>63</v>
+        <v>21.3482850990073</v>
       </c>
       <c r="K5" t="n">
-        <v>272</v>
+        <v>9</v>
       </c>
       <c r="L5" t="n">
+        <v>9.18</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="N5" t="n">
+        <v>110</v>
+      </c>
+      <c r="O5" t="n">
+        <v>108</v>
+      </c>
+      <c r="P5" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>87</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
         <v>100</v>
       </c>
-      <c r="M5" t="n">
-        <v>81.87</v>
-      </c>
-      <c r="N5" t="n">
-        <v>100</v>
-      </c>
-      <c r="O5" t="n">
-        <v>103.01</v>
-      </c>
-      <c r="P5" t="n">
-        <v>10.67</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>110</v>
-      </c>
-      <c r="S5" t="n">
-        <v>108</v>
-      </c>
-      <c r="T5" t="n">
-        <v>67.69</v>
-      </c>
       <c r="U5" t="n">
+        <v>82.33</v>
+      </c>
+      <c r="V5" t="n">
         <v>12</v>
       </c>
-      <c r="V5" t="n">
+      <c r="W5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1568,7 +1652,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>EFG</t>
+          <t>ESG-Fx</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1577,60 +1661,63 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3546084</v>
+        <v>212702.92</v>
       </c>
       <c r="E6" t="n">
-        <v>3402384.64</v>
+        <v>158341.77</v>
       </c>
       <c r="F6" t="n">
-        <v>122928.56</v>
+        <v>132249.57</v>
       </c>
       <c r="G6" t="n">
-        <v>16</v>
+        <v>11609.88</v>
       </c>
       <c r="H6" t="n">
-        <v>82522</v>
+        <v>14482.32</v>
       </c>
       <c r="I6" t="n">
-        <v>108882</v>
+        <v>27801.46</v>
       </c>
       <c r="J6" t="n">
-        <v>109090</v>
+        <v>21.0219662717996</v>
       </c>
       <c r="K6" t="n">
-        <v>541644</v>
+        <v>18</v>
       </c>
       <c r="L6" t="n">
-        <v>98.31778903903904</v>
+        <v>401.72</v>
       </c>
       <c r="M6" t="n">
-        <v>7975.959999999999</v>
+        <v>3.24</v>
       </c>
       <c r="N6" t="n">
-        <v>85.76730855855855</v>
+        <v>87850</v>
       </c>
       <c r="O6" t="n">
-        <v>12963.51</v>
+        <v>149694</v>
       </c>
       <c r="P6" t="n">
-        <v>907.6399999999999</v>
+        <v>68622</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.9</v>
+        <v>397950</v>
       </c>
       <c r="R6" t="n">
-        <v>87850</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>149694</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>8745.810000000001</v>
+        <v>100</v>
       </c>
       <c r="U6" t="n">
+        <v>25502.41</v>
+      </c>
+      <c r="V6" t="n">
         <v>2664</v>
       </c>
-      <c r="V6" t="n">
+      <c r="W6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1642,7 +1729,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>EFG</t>
+          <t>ESG-Fx</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1651,60 +1738,63 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>659659.42</v>
+        <v>57759.44</v>
       </c>
       <c r="E7" t="n">
-        <v>599331.26</v>
+        <v>38838.22</v>
       </c>
       <c r="F7" t="n">
-        <v>47558.88</v>
+        <v>31370.22</v>
       </c>
       <c r="G7" t="n">
-        <v>18.34</v>
+        <v>2699.41</v>
       </c>
       <c r="H7" t="n">
-        <v>11760</v>
+        <v>4768.59</v>
       </c>
       <c r="I7" t="n">
-        <v>14970</v>
+        <v>7451</v>
       </c>
       <c r="J7" t="n">
-        <v>19102</v>
+        <v>23.75182577616606</v>
       </c>
       <c r="K7" t="n">
-        <v>253983</v>
+        <v>19.74</v>
       </c>
       <c r="L7" t="n">
-        <v>92.25575000000001</v>
+        <v>125.11</v>
       </c>
       <c r="M7" t="n">
-        <v>9286.120000000001</v>
+        <v>3.03</v>
       </c>
       <c r="N7" t="n">
-        <v>92.56637500000001</v>
+        <v>12560</v>
       </c>
       <c r="O7" t="n">
-        <v>9586.73</v>
+        <v>15770</v>
       </c>
       <c r="P7" t="n">
-        <v>473.37</v>
+        <v>4611</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.69</v>
+        <v>119710</v>
       </c>
       <c r="R7" t="n">
-        <v>12560</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>15770</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3260.06</v>
+        <v>100</v>
       </c>
       <c r="U7" t="n">
+        <v>10925.75</v>
+      </c>
+      <c r="V7" t="n">
         <v>400</v>
       </c>
-      <c r="V7" t="n">
+      <c r="W7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1716,7 +1806,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>EFG</t>
+          <t>ESG-Fx</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1725,60 +1815,63 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>21771.56</v>
+        <v>5355.04</v>
       </c>
       <c r="E8" t="n">
-        <v>20185.07</v>
+        <v>3917.86</v>
       </c>
       <c r="F8" t="n">
-        <v>1088.4</v>
+        <v>3246.01</v>
       </c>
       <c r="G8" t="n">
-        <v>8</v>
+        <v>176.91</v>
       </c>
       <c r="H8" t="n">
-        <v>269</v>
+        <v>494.94</v>
       </c>
       <c r="I8" t="n">
-        <v>366</v>
+        <v>719.26</v>
       </c>
       <c r="J8" t="n">
-        <v>237</v>
+        <v>22.15828047356601</v>
       </c>
       <c r="K8" t="n">
-        <v>704</v>
+        <v>11</v>
       </c>
       <c r="L8" t="n">
-        <v>97.1182608695652</v>
+        <v>22.89</v>
       </c>
       <c r="M8" t="n">
-        <v>156.02</v>
+        <v>2.34</v>
       </c>
       <c r="N8" t="n">
-        <v>75.06913043478261</v>
+        <v>315</v>
       </c>
       <c r="O8" t="n">
-        <v>280.41</v>
+        <v>587</v>
       </c>
       <c r="P8" t="n">
-        <v>19.8</v>
+        <v>322</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.11</v>
+        <v>1561</v>
       </c>
       <c r="R8" t="n">
-        <v>315</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>587</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>218.39</v>
+        <v>100</v>
       </c>
       <c r="U8" t="n">
+        <v>689.27</v>
+      </c>
+      <c r="V8" t="n">
         <v>23</v>
       </c>
-      <c r="V8" t="n">
+      <c r="W8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1790,7 +1883,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>EFG</t>
+          <t>ESG-Fx</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1799,60 +1892,63 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1294199.46</v>
+        <v>1485963.2</v>
       </c>
       <c r="E9" t="n">
-        <v>861791.9299999999</v>
+        <v>1235221.05</v>
       </c>
       <c r="F9" t="n">
-        <v>405481.66</v>
+        <v>1197479.47</v>
       </c>
       <c r="G9" t="n">
-        <v>43.66</v>
+        <v>13175.53</v>
       </c>
       <c r="H9" t="n">
-        <v>72550</v>
+        <v>24566.05</v>
       </c>
       <c r="I9" t="n">
-        <v>195587</v>
+        <v>150121.31</v>
       </c>
       <c r="J9" t="n">
-        <v>20131</v>
+        <v>12.53644123017825</v>
       </c>
       <c r="K9" t="n">
-        <v>91266</v>
+        <v>260.17</v>
       </c>
       <c r="L9" t="n">
-        <v>16.259</v>
+        <v>466.14</v>
       </c>
       <c r="M9" t="n">
-        <v>3832.62</v>
+        <v>9.68</v>
       </c>
       <c r="N9" t="n">
-        <v>6.967750000000001</v>
+        <v>73350</v>
       </c>
       <c r="O9" t="n">
-        <v>13723.8</v>
+        <v>210644</v>
       </c>
       <c r="P9" t="n">
-        <v>361.57</v>
+        <v>140363</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.07</v>
+        <v>1241003</v>
       </c>
       <c r="R9" t="n">
-        <v>73350</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>210644</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>10888.3</v>
+        <v>100</v>
       </c>
       <c r="U9" t="n">
+        <v>100071.94</v>
+      </c>
+      <c r="V9" t="n">
         <v>400</v>
       </c>
-      <c r="V9" t="n">
+      <c r="W9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1867,118 +1963,148 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V9"/>
+  <dimension ref="A1:W9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="27" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="23" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
+    <col width="25" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="31" customWidth="1" min="19" max="19"/>
+    <col width="17" customWidth="1" min="20" max="20"/>
+    <col width="30" customWidth="1" min="21" max="21"/>
+    <col width="19" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="23" max="23"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>SPL Name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Approach</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Coverage Type</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Total Elapsed Time(ms)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Total TestGenTime(ms)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Total Parse Time (ms)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Total TestGenPeakMemory(MB)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Total NumberOfEFGVertices</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Total NumberOfEFGEdges</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Total NumberOfEFGTestCases</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Total NumberOfEFGTestEvents</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Event Coverage(%)</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Event Coverage Analysis Time(ms)</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Edge Coverage(%)</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Edge Coverage Analysis Time(ms)</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Total TestExecTime(ms)</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Total TestExecPeakMemory(MB)</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Total ESGFx_Vertices</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Total ESGFx_Edges</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Total ESGFxModelLoadTimeMs</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Processed Products</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Failed Products</t>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>TotalElapsedTime(ms)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>TotalTestGenTime(ms)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>AlgTestGenTime(ms)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ESGFxModelLoadTime(ms)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>TestCaseRecordingTime(ms)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>TransformationTime(ms)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>TransformationShare(%)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>TestGenPeakMemory(MB)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>TestExecTime(ms)</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>TestExecPeakMemory(MB)</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>NumberOfESGFxVertices</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>NumberOfESGFxEdges</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>NumberOfESGFxTestCases</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>NumberOfESGFxTestEvents</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>EventCoverage(%)</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>EventCoverageAnalysisTime(ms)</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>EdgeCoverage(%)</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>EdgeCoverageAnalysisTime(ms)</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>ProcessedProducts</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>FailedProducts</t>
         </is>
       </c>
     </row>
@@ -1990,7 +2116,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>EFG</t>
+          <t>ESG-Fx</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1999,60 +2125,63 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>707441.1899999999</v>
+        <v>37515.96</v>
       </c>
       <c r="E2" t="n">
-        <v>667225.2100000001</v>
+        <v>26529.64</v>
       </c>
       <c r="F2" t="n">
-        <v>33897.28</v>
+        <v>20962.98</v>
       </c>
       <c r="G2" t="n">
-        <v>10</v>
+        <v>2907.9</v>
       </c>
       <c r="H2" t="n">
-        <v>11664</v>
+        <v>2658.76</v>
       </c>
       <c r="I2" t="n">
-        <v>9939</v>
+        <v>7461.85</v>
       </c>
       <c r="J2" t="n">
-        <v>5883</v>
+        <v>35.59536859740361</v>
       </c>
       <c r="K2" t="n">
-        <v>22374</v>
+        <v>11</v>
       </c>
       <c r="L2" t="n">
-        <v>100</v>
+        <v>101.38</v>
       </c>
       <c r="M2" t="n">
-        <v>1928.3</v>
+        <v>2.71</v>
       </c>
       <c r="N2" t="n">
-        <v>98.80202811244979</v>
+        <v>12660</v>
       </c>
       <c r="O2" t="n">
-        <v>2918.01</v>
+        <v>16395</v>
       </c>
       <c r="P2" t="n">
-        <v>192.11</v>
+        <v>4218</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.59</v>
+        <v>9492</v>
       </c>
       <c r="R2" t="n">
-        <v>12660</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>16395</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>3380.58</v>
+        <v>91.59991967871487</v>
       </c>
       <c r="U2" t="n">
+        <v>3352.56</v>
+      </c>
+      <c r="V2" t="n">
         <v>498</v>
       </c>
-      <c r="V2" t="n">
+      <c r="W2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2064,7 +2193,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>EFG</t>
+          <t>ESG-Fx</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2073,60 +2202,63 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>50268.67</v>
+        <v>24908.86</v>
       </c>
       <c r="E3" t="n">
-        <v>42370.22</v>
+        <v>18783.74</v>
       </c>
       <c r="F3" t="n">
-        <v>5794.99</v>
+        <v>16974.32</v>
       </c>
       <c r="G3" t="n">
-        <v>12</v>
+        <v>491.84</v>
       </c>
       <c r="H3" t="n">
-        <v>470</v>
+        <v>1317.58</v>
       </c>
       <c r="I3" t="n">
-        <v>1144</v>
+        <v>3142.92</v>
       </c>
       <c r="J3" t="n">
-        <v>2768</v>
+        <v>18.51573435636892</v>
       </c>
       <c r="K3" t="n">
-        <v>11218</v>
+        <v>31.86</v>
       </c>
       <c r="L3" t="n">
+        <v>39.24</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="N3" t="n">
+        <v>554</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1566</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3360</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>5854</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
         <v>100</v>
       </c>
-      <c r="M3" t="n">
-        <v>1472.9</v>
-      </c>
-      <c r="N3" t="n">
-        <v>100</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1482.2</v>
-      </c>
-      <c r="P3" t="n">
-        <v>73.59999999999999</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="R3" t="n">
-        <v>554</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1566</v>
-      </c>
-      <c r="T3" t="n">
-        <v>469.75</v>
-      </c>
       <c r="U3" t="n">
+        <v>2790</v>
+      </c>
+      <c r="V3" t="n">
         <v>42</v>
       </c>
-      <c r="V3" t="n">
+      <c r="W3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2138,7 +2270,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EFG</t>
+          <t>ESG-Fx</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2147,60 +2279,63 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>793675.9099999999</v>
+        <v>95316.54999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>709146.3</v>
+        <v>61178.77999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>68705.71000000001</v>
+        <v>50196.64999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>18</v>
+        <v>3911.2</v>
       </c>
       <c r="H4" t="n">
-        <v>24985</v>
+        <v>7070.93</v>
       </c>
       <c r="I4" t="n">
-        <v>28895</v>
+        <v>17348.23</v>
       </c>
       <c r="J4" t="n">
-        <v>19134</v>
+        <v>34.56053342205108</v>
       </c>
       <c r="K4" t="n">
-        <v>248570</v>
+        <v>20.94</v>
       </c>
       <c r="L4" t="n">
-        <v>39.00603365384615</v>
+        <v>201.17</v>
       </c>
       <c r="M4" t="n">
-        <v>5403.93</v>
+        <v>3.25</v>
       </c>
       <c r="N4" t="n">
-        <v>40.29302884615385</v>
+        <v>25817</v>
       </c>
       <c r="O4" t="n">
-        <v>9143.610000000001</v>
+        <v>29727</v>
       </c>
       <c r="P4" t="n">
-        <v>500.49</v>
+        <v>4618</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.95</v>
+        <v>218547</v>
       </c>
       <c r="R4" t="n">
-        <v>25817</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>29727</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>5025.57</v>
+        <v>100</v>
       </c>
       <c r="U4" t="n">
+        <v>16492.24</v>
+      </c>
+      <c r="V4" t="n">
         <v>416</v>
       </c>
-      <c r="V4" t="n">
+      <c r="W4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2212,7 +2347,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>EFG</t>
+          <t>ESG-Fx</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2221,60 +2356,63 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11911.92</v>
+        <v>1878.87</v>
       </c>
       <c r="E5" t="n">
-        <v>11171.19</v>
+        <v>1480.78</v>
       </c>
       <c r="F5" t="n">
-        <v>538.45</v>
+        <v>1097.85</v>
       </c>
       <c r="G5" t="n">
-        <v>8</v>
+        <v>48.81</v>
       </c>
       <c r="H5" t="n">
-        <v>86</v>
+        <v>334.12</v>
       </c>
       <c r="I5" t="n">
-        <v>78</v>
+        <v>264.31</v>
       </c>
       <c r="J5" t="n">
-        <v>46</v>
+        <v>24.07523796511363</v>
       </c>
       <c r="K5" t="n">
-        <v>229</v>
+        <v>9</v>
       </c>
       <c r="L5" t="n">
+        <v>9.56</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="N5" t="n">
+        <v>110</v>
+      </c>
+      <c r="O5" t="n">
+        <v>108</v>
+      </c>
+      <c r="P5" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>65</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
         <v>100</v>
       </c>
-      <c r="M5" t="n">
-        <v>65.03</v>
-      </c>
-      <c r="N5" t="n">
-        <v>100</v>
-      </c>
-      <c r="O5" t="n">
-        <v>87.57000000000001</v>
-      </c>
-      <c r="P5" t="n">
-        <v>10.33</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>110</v>
-      </c>
-      <c r="S5" t="n">
-        <v>108</v>
-      </c>
-      <c r="T5" t="n">
-        <v>60.77</v>
-      </c>
       <c r="U5" t="n">
+        <v>87.83</v>
+      </c>
+      <c r="V5" t="n">
         <v>12</v>
       </c>
-      <c r="V5" t="n">
+      <c r="W5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2286,7 +2424,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>EFG</t>
+          <t>ESG-Fx</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2295,60 +2433,63 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3716421.42</v>
+        <v>401939.41</v>
       </c>
       <c r="E6" t="n">
-        <v>3542691.54</v>
+        <v>292764.42</v>
       </c>
       <c r="F6" t="n">
-        <v>145523.36</v>
+        <v>253821.64</v>
       </c>
       <c r="G6" t="n">
-        <v>17</v>
+        <v>13390.8</v>
       </c>
       <c r="H6" t="n">
-        <v>82522</v>
+        <v>25551.98</v>
       </c>
       <c r="I6" t="n">
-        <v>108882</v>
+        <v>55530.78</v>
       </c>
       <c r="J6" t="n">
-        <v>132636</v>
+        <v>21.87787455789822</v>
       </c>
       <c r="K6" t="n">
-        <v>740822</v>
+        <v>24</v>
       </c>
       <c r="L6" t="n">
+        <v>449.65</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N6" t="n">
+        <v>87850</v>
+      </c>
+      <c r="O6" t="n">
+        <v>149694</v>
+      </c>
+      <c r="P6" t="n">
+        <v>117192</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>654272</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
         <v>100</v>
       </c>
-      <c r="M6" t="n">
-        <v>9718.25</v>
-      </c>
-      <c r="N6" t="n">
-        <v>86.93719219219219</v>
-      </c>
-      <c r="O6" t="n">
-        <v>15281.73</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1047.91</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="R6" t="n">
-        <v>87850</v>
-      </c>
-      <c r="S6" t="n">
-        <v>149694</v>
-      </c>
-      <c r="T6" t="n">
-        <v>8523.639999999999</v>
-      </c>
       <c r="U6" t="n">
+        <v>51217.07</v>
+      </c>
+      <c r="V6" t="n">
         <v>2664</v>
       </c>
-      <c r="V6" t="n">
+      <c r="W6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2360,7 +2501,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>EFG</t>
+          <t>ESG-Fx</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2369,60 +2510,63 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>687461.8600000001</v>
+        <v>75923.48</v>
       </c>
       <c r="E7" t="n">
-        <v>614102.8999999999</v>
+        <v>49122.93</v>
       </c>
       <c r="F7" t="n">
-        <v>58138.72</v>
+        <v>40081.91</v>
       </c>
       <c r="G7" t="n">
-        <v>28.36</v>
+        <v>2917.71</v>
       </c>
       <c r="H7" t="n">
-        <v>11760</v>
+        <v>6123.309999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>14970</v>
+        <v>11276.21</v>
       </c>
       <c r="J7" t="n">
-        <v>24682</v>
+        <v>28.13291582162626</v>
       </c>
       <c r="K7" t="n">
-        <v>338669</v>
+        <v>38.25</v>
       </c>
       <c r="L7" t="n">
-        <v>92.25575000000001</v>
+        <v>125.39</v>
       </c>
       <c r="M7" t="n">
-        <v>10952.68</v>
+        <v>3.56</v>
       </c>
       <c r="N7" t="n">
-        <v>92.56637500000001</v>
+        <v>12560</v>
       </c>
       <c r="O7" t="n">
-        <v>11115.1</v>
+        <v>15770</v>
       </c>
       <c r="P7" t="n">
-        <v>528.71</v>
+        <v>5673</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.73</v>
+        <v>143125</v>
       </c>
       <c r="R7" t="n">
-        <v>12560</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>15770</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3200.75</v>
+        <v>100</v>
       </c>
       <c r="U7" t="n">
+        <v>15318.95</v>
+      </c>
+      <c r="V7" t="n">
         <v>400</v>
       </c>
-      <c r="V7" t="n">
+      <c r="W7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2434,7 +2578,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>EFG</t>
+          <t>ESG-Fx</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2443,60 +2587,63 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>23364.71</v>
+        <v>10641.26</v>
       </c>
       <c r="E8" t="n">
-        <v>21421.51</v>
+        <v>7304.6</v>
       </c>
       <c r="F8" t="n">
-        <v>1480.96</v>
+        <v>6413.43</v>
       </c>
       <c r="G8" t="n">
-        <v>9</v>
+        <v>224.68</v>
       </c>
       <c r="H8" t="n">
-        <v>269</v>
+        <v>666.49</v>
       </c>
       <c r="I8" t="n">
-        <v>366</v>
+        <v>1455.27</v>
       </c>
       <c r="J8" t="n">
-        <v>408</v>
+        <v>22.69097815053723</v>
       </c>
       <c r="K8" t="n">
-        <v>1567</v>
+        <v>15</v>
       </c>
       <c r="L8" t="n">
-        <v>100</v>
+        <v>23.27</v>
       </c>
       <c r="M8" t="n">
-        <v>253.46</v>
+        <v>2.55</v>
       </c>
       <c r="N8" t="n">
-        <v>82.08086956521738</v>
+        <v>315</v>
       </c>
       <c r="O8" t="n">
-        <v>423.76</v>
+        <v>587</v>
       </c>
       <c r="P8" t="n">
-        <v>24.41</v>
+        <v>793</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.12</v>
+        <v>4031</v>
       </c>
       <c r="R8" t="n">
-        <v>315</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>587</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>192.1</v>
+        <v>96.47739130434783</v>
       </c>
       <c r="U8" t="n">
+        <v>1780.64</v>
+      </c>
+      <c r="V8" t="n">
         <v>23</v>
       </c>
-      <c r="V8" t="n">
+      <c r="W8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2508,7 +2655,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>EFG</t>
+          <t>ESG-Fx</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2517,60 +2664,63 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1403184.85</v>
+        <v>2471757.77</v>
       </c>
       <c r="E9" t="n">
-        <v>923838.34</v>
+        <v>2059616.82</v>
       </c>
       <c r="F9" t="n">
-        <v>451260.28</v>
+        <v>2022030.65</v>
       </c>
       <c r="G9" t="n">
-        <v>50.69</v>
+        <v>11744.82</v>
       </c>
       <c r="H9" t="n">
-        <v>72550</v>
+        <v>25841.35</v>
       </c>
       <c r="I9" t="n">
-        <v>195587</v>
+        <v>283572.01</v>
       </c>
       <c r="J9" t="n">
-        <v>43556</v>
+        <v>14.02412025752429</v>
       </c>
       <c r="K9" t="n">
-        <v>240836</v>
+        <v>454.09</v>
       </c>
       <c r="L9" t="n">
-        <v>20.14675</v>
+        <v>376.52</v>
       </c>
       <c r="M9" t="n">
-        <v>6581.9</v>
+        <v>23.03</v>
       </c>
       <c r="N9" t="n">
-        <v>10.455875</v>
+        <v>73350</v>
       </c>
       <c r="O9" t="n">
-        <v>18629.5</v>
+        <v>210644</v>
       </c>
       <c r="P9" t="n">
-        <v>598.29</v>
+        <v>193641</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.09</v>
+        <v>1606648</v>
       </c>
       <c r="R9" t="n">
-        <v>73350</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>210644</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>11039.57</v>
+        <v>100</v>
       </c>
       <c r="U9" t="n">
+        <v>126036.15</v>
+      </c>
+      <c r="V9" t="n">
         <v>400</v>
       </c>
-      <c r="V9" t="n">
+      <c r="W9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2585,103 +2735,142 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S9"/>
+  <dimension ref="A1:V9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="23" customWidth="1" min="15" max="15"/>
+    <col width="17" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="31" customWidth="1" min="18" max="18"/>
+    <col width="17" customWidth="1" min="19" max="19"/>
+    <col width="30" customWidth="1" min="20" max="20"/>
+    <col width="19" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>SPL Name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Approach</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Coverage Type</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Total Elapsed Time(ms)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Edge Coverage(%)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Processed Products</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Failed Products</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Test Generation Time(ms)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Test Generation Peak Memory(MB)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Number of ESGFx Vertices</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Number of ESGFx Edges</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Number of ESGFx Test Cases</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Number of ESGFx Test Events</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Test Case Recording Time(ms)</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Test Execution Time(ms)</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Test Execution Peak Memory(MB)</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>ESGFx Model Load Time(ms)</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Transformation Time(ms)</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Coverage Analysis Time(ms)</t>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>TotalElapsedTime(ms)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>GuitarGenTime(ms)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>TestGenPeakMemory(MB)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>TestExecTime(ms)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>TestExecPeakMemory(MB)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ESGFxModelLoadTime(ms)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>NumberOfESGFxVertices</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>NumberOfESGFxEdges</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>NumberOfEFGVertices</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>NumberOfEFGEdges</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>NumberOfEFGTestCases</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>NumberOfEFGTestEvents</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>ParsingTime(ms)</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>EventCoverage(%)</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>EventCoverageAnalysisTime(ms)</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>EdgeCoverage(%)</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>EdgeCoverageAnalysisTime(ms)</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>ProcessedProducts</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>FailedProducts</t>
         </is>
       </c>
     </row>
@@ -2693,7 +2882,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ESG-Fx</t>
+          <t>EFG</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2702,22 +2891,22 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>26267.36</v>
+        <v>701477.47</v>
       </c>
       <c r="E2" t="n">
-        <v>100</v>
+        <v>664279.5900000001</v>
       </c>
       <c r="F2" t="n">
-        <v>498</v>
+        <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>242.08</v>
       </c>
       <c r="H2" t="n">
-        <v>15850</v>
+        <v>2.6</v>
       </c>
       <c r="I2" t="n">
-        <v>11</v>
+        <v>3516.51</v>
       </c>
       <c r="J2" t="n">
         <v>12660</v>
@@ -2726,28 +2915,37 @@
         <v>16395</v>
       </c>
       <c r="L2" t="n">
-        <v>4407</v>
+        <v>11664</v>
       </c>
       <c r="M2" t="n">
-        <v>16506</v>
+        <v>9939</v>
       </c>
       <c r="N2" t="n">
-        <v>2563.29</v>
+        <v>9507</v>
       </c>
       <c r="O2" t="n">
-        <v>128.77</v>
+        <v>29892</v>
       </c>
       <c r="P2" t="n">
-        <v>2.7</v>
+        <v>29944.23</v>
       </c>
       <c r="Q2" t="n">
-        <v>2873.1</v>
+        <v>98.34198795180724</v>
       </c>
       <c r="R2" t="n">
-        <v>2117.71</v>
+        <v>2093.96</v>
       </c>
       <c r="S2" t="n">
-        <v>2793.43</v>
+        <v>96.40536144578313</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3267.84</v>
+      </c>
+      <c r="U2" t="n">
+        <v>498</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -2758,7 +2956,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ESG-Fx</t>
+          <t>EFG</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2767,22 +2965,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>7183.879999999999</v>
+        <v>44353.24</v>
       </c>
       <c r="E3" t="n">
-        <v>100</v>
+        <v>40288.09</v>
       </c>
       <c r="F3" t="n">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>44.75</v>
       </c>
       <c r="H3" t="n">
-        <v>4613.86</v>
+        <v>2.14</v>
       </c>
       <c r="I3" t="n">
-        <v>11</v>
+        <v>456.04</v>
       </c>
       <c r="J3" t="n">
         <v>554</v>
@@ -2791,28 +2989,37 @@
         <v>1566</v>
       </c>
       <c r="L3" t="n">
-        <v>651</v>
+        <v>470</v>
       </c>
       <c r="M3" t="n">
-        <v>1994</v>
+        <v>1144</v>
       </c>
       <c r="N3" t="n">
-        <v>805.28</v>
+        <v>1120</v>
       </c>
       <c r="O3" t="n">
-        <v>33.96</v>
+        <v>3178</v>
       </c>
       <c r="P3" t="n">
-        <v>2.33</v>
+        <v>2907.59</v>
       </c>
       <c r="Q3" t="n">
-        <v>367.15</v>
+        <v>100</v>
       </c>
       <c r="R3" t="n">
-        <v>560.5999999999999</v>
+        <v>476.65</v>
       </c>
       <c r="S3" t="n">
-        <v>703.45</v>
+        <v>98.1054761904762</v>
+      </c>
+      <c r="T3" t="n">
+        <v>872.0200000000001</v>
+      </c>
+      <c r="U3" t="n">
+        <v>42</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -2823,7 +3030,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ESG-Fx</t>
+          <t>EFG</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2832,22 +3039,22 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>42054.7</v>
+        <v>749836.8500000001</v>
       </c>
       <c r="E4" t="n">
-        <v>100</v>
+        <v>684224.61</v>
       </c>
       <c r="F4" t="n">
-        <v>416</v>
+        <v>17</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>344.66</v>
       </c>
       <c r="H4" t="n">
-        <v>24746.52</v>
+        <v>2.94</v>
       </c>
       <c r="I4" t="n">
-        <v>15</v>
+        <v>5065</v>
       </c>
       <c r="J4" t="n">
         <v>25817</v>
@@ -2856,28 +3063,37 @@
         <v>29727</v>
       </c>
       <c r="L4" t="n">
-        <v>2949</v>
+        <v>24985</v>
       </c>
       <c r="M4" t="n">
-        <v>149487</v>
+        <v>28895</v>
       </c>
       <c r="N4" t="n">
-        <v>4116.1</v>
+        <v>10931</v>
       </c>
       <c r="O4" t="n">
-        <v>310.83</v>
+        <v>122939</v>
       </c>
       <c r="P4" t="n">
-        <v>3.12</v>
+        <v>54302.03999999999</v>
       </c>
       <c r="Q4" t="n">
-        <v>3616.42</v>
+        <v>35.43786057692308</v>
       </c>
       <c r="R4" t="n">
-        <v>2836.42</v>
+        <v>3283.37</v>
       </c>
       <c r="S4" t="n">
-        <v>6212.360000000001</v>
+        <v>37.40694711538462</v>
+      </c>
+      <c r="T4" t="n">
+        <v>6418.12</v>
+      </c>
+      <c r="U4" t="n">
+        <v>416</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2888,7 +3104,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ESG-Fx</t>
+          <t>EFG</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2897,22 +3113,22 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1633.2</v>
+        <v>12632.47</v>
       </c>
       <c r="E5" t="n">
-        <v>100</v>
+        <v>11998.43</v>
       </c>
       <c r="F5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>11.06</v>
       </c>
       <c r="H5" t="n">
-        <v>957.2299999999999</v>
+        <v>2.1</v>
       </c>
       <c r="I5" t="n">
-        <v>9</v>
+        <v>75.12</v>
       </c>
       <c r="J5" t="n">
         <v>110</v>
@@ -2921,28 +3137,37 @@
         <v>108</v>
       </c>
       <c r="L5" t="n">
-        <v>22</v>
+        <v>86</v>
       </c>
       <c r="M5" t="n">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="N5" t="n">
-        <v>333.25</v>
+        <v>78</v>
       </c>
       <c r="O5" t="n">
-        <v>9.09</v>
+        <v>294</v>
       </c>
       <c r="P5" t="n">
-        <v>2.22</v>
+        <v>487.32</v>
       </c>
       <c r="Q5" t="n">
-        <v>43.56999999999999</v>
+        <v>100</v>
       </c>
       <c r="R5" t="n">
-        <v>150.82</v>
+        <v>78.44999999999999</v>
       </c>
       <c r="S5" t="n">
-        <v>68.05</v>
+        <v>100</v>
+      </c>
+      <c r="T5" t="n">
+        <v>90.59</v>
+      </c>
+      <c r="U5" t="n">
+        <v>12</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -2953,7 +3178,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ESG-Fx</t>
+          <t>EFG</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2962,22 +3187,22 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>99029.62</v>
+        <v>3426157.82</v>
       </c>
       <c r="E6" t="n">
-        <v>100</v>
+        <v>3303437.810000001</v>
       </c>
       <c r="F6" t="n">
-        <v>2664</v>
+        <v>15</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>759.6399999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>59598.64</v>
+        <v>2.9</v>
       </c>
       <c r="I6" t="n">
-        <v>15</v>
+        <v>8671.389999999999</v>
       </c>
       <c r="J6" t="n">
         <v>87850</v>
@@ -2986,28 +3211,37 @@
         <v>149694</v>
       </c>
       <c r="L6" t="n">
-        <v>38236</v>
+        <v>82522</v>
       </c>
       <c r="M6" t="n">
-        <v>244862</v>
+        <v>108882</v>
       </c>
       <c r="N6" t="n">
-        <v>9184.129999999999</v>
+        <v>83870</v>
       </c>
       <c r="O6" t="n">
-        <v>648.1800000000001</v>
+        <v>353670</v>
       </c>
       <c r="P6" t="n">
-        <v>3.07</v>
+        <v>102641.76</v>
       </c>
       <c r="Q6" t="n">
-        <v>10789.87</v>
+        <v>93.18321321321322</v>
       </c>
       <c r="R6" t="n">
-        <v>5528.9</v>
+        <v>5843.58</v>
       </c>
       <c r="S6" t="n">
-        <v>13234.34</v>
+        <v>68.80961336336337</v>
+      </c>
+      <c r="T6" t="n">
+        <v>10806.84</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2664</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -3018,7 +3252,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ESG-Fx</t>
+          <t>EFG</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3027,22 +3261,22 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>33732.66</v>
+        <v>629489.51</v>
       </c>
       <c r="E7" t="n">
-        <v>100</v>
+        <v>579951.01</v>
       </c>
       <c r="F7" t="n">
-        <v>400</v>
+        <v>13.31</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>434.49</v>
       </c>
       <c r="H7" t="n">
-        <v>19662.1</v>
+        <v>2.67</v>
       </c>
       <c r="I7" t="n">
-        <v>13</v>
+        <v>3221.92</v>
       </c>
       <c r="J7" t="n">
         <v>12560</v>
@@ -3051,28 +3285,37 @@
         <v>15770</v>
       </c>
       <c r="L7" t="n">
-        <v>2910</v>
+        <v>11760</v>
       </c>
       <c r="M7" t="n">
-        <v>77553</v>
+        <v>14970</v>
       </c>
       <c r="N7" t="n">
-        <v>3609.809999999999</v>
+        <v>14390</v>
       </c>
       <c r="O7" t="n">
-        <v>256.25</v>
+        <v>186754</v>
       </c>
       <c r="P7" t="n">
-        <v>2.82</v>
+        <v>38695.74000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>2420.1</v>
+        <v>92.25575000000001</v>
       </c>
       <c r="R7" t="n">
-        <v>2091.02</v>
+        <v>7454.22</v>
       </c>
       <c r="S7" t="n">
-        <v>5885.52</v>
+        <v>92.56637500000001</v>
+      </c>
+      <c r="T7" t="n">
+        <v>8215.790000000001</v>
+      </c>
+      <c r="U7" t="n">
+        <v>400</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -3083,7 +3326,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ESG-Fx</t>
+          <t>EFG</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3092,22 +3335,22 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3396.57</v>
+        <v>22844.7</v>
       </c>
       <c r="E8" t="n">
-        <v>100</v>
+        <v>21542.64</v>
       </c>
       <c r="F8" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>18.16</v>
       </c>
       <c r="H8" t="n">
-        <v>2205.55</v>
+        <v>2.11</v>
       </c>
       <c r="I8" t="n">
-        <v>10</v>
+        <v>190.4</v>
       </c>
       <c r="J8" t="n">
         <v>315</v>
@@ -3116,28 +3359,37 @@
         <v>587</v>
       </c>
       <c r="L8" t="n">
-        <v>138</v>
+        <v>269</v>
       </c>
       <c r="M8" t="n">
-        <v>634</v>
+        <v>366</v>
       </c>
       <c r="N8" t="n">
-        <v>411.61</v>
+        <v>156</v>
       </c>
       <c r="O8" t="n">
-        <v>19.33</v>
+        <v>348</v>
       </c>
       <c r="P8" t="n">
-        <v>2.29</v>
+        <v>842.05</v>
       </c>
       <c r="Q8" t="n">
-        <v>167.93</v>
+        <v>80.05173913043478</v>
       </c>
       <c r="R8" t="n">
-        <v>303.54</v>
+        <v>115.14</v>
       </c>
       <c r="S8" t="n">
-        <v>289.45</v>
+        <v>35.75304347826086</v>
+      </c>
+      <c r="T8" t="n">
+        <v>227.54</v>
+      </c>
+      <c r="U8" t="n">
+        <v>23</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -3148,7 +3400,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ESG-Fx</t>
+          <t>EFG</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3157,22 +3409,22 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>713062.16</v>
+        <v>1207824.08</v>
       </c>
       <c r="E9" t="n">
-        <v>100</v>
+        <v>809451.26</v>
       </c>
       <c r="F9" t="n">
-        <v>400</v>
+        <v>40.67</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>193</v>
       </c>
       <c r="H9" t="n">
-        <v>611119.5600000001</v>
+        <v>3.06</v>
       </c>
       <c r="I9" t="n">
-        <v>127.66</v>
+        <v>10802.15</v>
       </c>
       <c r="J9" t="n">
         <v>73350</v>
@@ -3181,28 +3433,37 @@
         <v>210644</v>
       </c>
       <c r="L9" t="n">
-        <v>118564</v>
+        <v>72550</v>
       </c>
       <c r="M9" t="n">
-        <v>1137997</v>
+        <v>195587</v>
       </c>
       <c r="N9" t="n">
-        <v>20192.82</v>
+        <v>8293</v>
       </c>
       <c r="O9" t="n">
-        <v>1064.01</v>
+        <v>28756</v>
       </c>
       <c r="P9" t="n">
-        <v>4.67</v>
+        <v>377991.71</v>
       </c>
       <c r="Q9" t="n">
-        <v>14492.28</v>
+        <v>8.482624999999999</v>
       </c>
       <c r="R9" t="n">
-        <v>7342.95</v>
+        <v>2590.47</v>
       </c>
       <c r="S9" t="n">
-        <v>59027.81</v>
+        <v>4.095125</v>
+      </c>
+      <c r="T9" t="n">
+        <v>11191.51</v>
+      </c>
+      <c r="U9" t="n">
+        <v>400</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3216,103 +3477,142 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S9"/>
+  <dimension ref="A1:V9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="23" customWidth="1" min="15" max="15"/>
+    <col width="17" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="31" customWidth="1" min="18" max="18"/>
+    <col width="17" customWidth="1" min="19" max="19"/>
+    <col width="30" customWidth="1" min="20" max="20"/>
+    <col width="19" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>SPL Name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Approach</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Coverage Type</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Total Elapsed Time(ms)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Edge Coverage(%)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Processed Products</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Failed Products</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Test Generation Time(ms)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Test Generation Peak Memory(MB)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Number of ESGFx Vertices</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Number of ESGFx Edges</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Number of ESGFx Test Cases</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Number of ESGFx Test Events</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Test Case Recording Time(ms)</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Test Execution Time(ms)</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Test Execution Peak Memory(MB)</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>ESGFx Model Load Time(ms)</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Transformation Time(ms)</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Coverage Analysis Time(ms)</t>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>TotalElapsedTime(ms)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>GuitarGenTime(ms)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>TestGenPeakMemory(MB)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>TestExecTime(ms)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>TestExecPeakMemory(MB)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ESGFxModelLoadTime(ms)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>NumberOfESGFxVertices</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>NumberOfESGFxEdges</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>NumberOfEFGVertices</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>NumberOfEFGEdges</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>NumberOfEFGTestCases</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>NumberOfEFGTestEvents</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>ParsingTime(ms)</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>EventCoverage(%)</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>EventCoverageAnalysisTime(ms)</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>EdgeCoverage(%)</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>EdgeCoverageAnalysisTime(ms)</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>ProcessedProducts</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>FailedProducts</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3624,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ESG-Fx</t>
+          <t>EFG</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3333,22 +3633,22 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>36947.39999999999</v>
+        <v>701119.02</v>
       </c>
       <c r="E2" t="n">
-        <v>100</v>
+        <v>662942.1599999999</v>
       </c>
       <c r="F2" t="n">
-        <v>498</v>
+        <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>223.03</v>
       </c>
       <c r="H2" t="n">
-        <v>21625.19</v>
+        <v>2.59</v>
       </c>
       <c r="I2" t="n">
-        <v>11</v>
+        <v>3342.26</v>
       </c>
       <c r="J2" t="n">
         <v>12660</v>
@@ -3357,28 +3657,37 @@
         <v>16395</v>
       </c>
       <c r="L2" t="n">
-        <v>4983</v>
+        <v>11664</v>
       </c>
       <c r="M2" t="n">
-        <v>14043</v>
+        <v>9939</v>
       </c>
       <c r="N2" t="n">
-        <v>2793.8</v>
+        <v>7485</v>
       </c>
       <c r="O2" t="n">
-        <v>124.86</v>
+        <v>26640</v>
       </c>
       <c r="P2" t="n">
-        <v>2.72</v>
+        <v>31777.74</v>
       </c>
       <c r="Q2" t="n">
-        <v>3003.81</v>
+        <v>99.44692771084335</v>
       </c>
       <c r="R2" t="n">
-        <v>5977.91</v>
+        <v>1986.23</v>
       </c>
       <c r="S2" t="n">
-        <v>3419.54</v>
+        <v>97.60373493975904</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3076.07</v>
+      </c>
+      <c r="U2" t="n">
+        <v>498</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -3389,7 +3698,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ESG-Fx</t>
+          <t>EFG</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3398,22 +3707,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15667.65</v>
+        <v>48608.57</v>
       </c>
       <c r="E3" t="n">
-        <v>100</v>
+        <v>41895.55</v>
       </c>
       <c r="F3" t="n">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>62.2</v>
       </c>
       <c r="H3" t="n">
-        <v>10143.67</v>
+        <v>2.15</v>
       </c>
       <c r="I3" t="n">
-        <v>16</v>
+        <v>426.45</v>
       </c>
       <c r="J3" t="n">
         <v>554</v>
@@ -3422,28 +3731,37 @@
         <v>1566</v>
       </c>
       <c r="L3" t="n">
-        <v>2063</v>
+        <v>470</v>
       </c>
       <c r="M3" t="n">
-        <v>4444</v>
+        <v>1144</v>
       </c>
       <c r="N3" t="n">
-        <v>1087.89</v>
+        <v>2184</v>
       </c>
       <c r="O3" t="n">
-        <v>36.78</v>
+        <v>7346</v>
       </c>
       <c r="P3" t="n">
-        <v>2.5</v>
+        <v>4725.77</v>
       </c>
       <c r="Q3" t="n">
-        <v>466.62</v>
+        <v>100</v>
       </c>
       <c r="R3" t="n">
-        <v>1851.1</v>
+        <v>998.08</v>
       </c>
       <c r="S3" t="n">
-        <v>1852.23</v>
+        <v>100</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1307.45</v>
+      </c>
+      <c r="U3" t="n">
+        <v>42</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -3454,7 +3772,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ESG-Fx</t>
+          <t>EFG</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3463,22 +3781,22 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>73187.89</v>
+        <v>770353.0900000001</v>
       </c>
       <c r="E4" t="n">
-        <v>100</v>
+        <v>695590.7399999999</v>
       </c>
       <c r="F4" t="n">
-        <v>416</v>
+        <v>17</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>435.29</v>
       </c>
       <c r="H4" t="n">
-        <v>39202.21</v>
+        <v>2.95</v>
       </c>
       <c r="I4" t="n">
-        <v>17</v>
+        <v>4849.84</v>
       </c>
       <c r="J4" t="n">
         <v>25817</v>
@@ -3487,28 +3805,37 @@
         <v>29727</v>
       </c>
       <c r="L4" t="n">
-        <v>4240</v>
+        <v>24985</v>
       </c>
       <c r="M4" t="n">
-        <v>205668</v>
+        <v>28895</v>
       </c>
       <c r="N4" t="n">
-        <v>6162.25</v>
+        <v>14938</v>
       </c>
       <c r="O4" t="n">
-        <v>207.77</v>
+        <v>182634</v>
       </c>
       <c r="P4" t="n">
-        <v>3.19</v>
+        <v>62171.34000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>3853.98</v>
+        <v>37.22170673076923</v>
       </c>
       <c r="R4" t="n">
-        <v>11460.6</v>
+        <v>4501.78</v>
       </c>
       <c r="S4" t="n">
-        <v>12436.78</v>
+        <v>38.85050480769231</v>
+      </c>
+      <c r="T4" t="n">
+        <v>7778.48</v>
+      </c>
+      <c r="U4" t="n">
+        <v>416</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -3519,7 +3846,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ESG-Fx</t>
+          <t>EFG</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3528,22 +3855,22 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1859.99</v>
+        <v>13007.22</v>
       </c>
       <c r="E5" t="n">
-        <v>100</v>
+        <v>12223.56</v>
       </c>
       <c r="F5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>10.67</v>
       </c>
       <c r="H5" t="n">
-        <v>1142.34</v>
+        <v>2.1</v>
       </c>
       <c r="I5" t="n">
-        <v>9</v>
+        <v>67.69</v>
       </c>
       <c r="J5" t="n">
         <v>110</v>
@@ -3552,28 +3879,37 @@
         <v>108</v>
       </c>
       <c r="L5" t="n">
-        <v>22</v>
+        <v>86</v>
       </c>
       <c r="M5" t="n">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N5" t="n">
-        <v>362.89</v>
+        <v>63</v>
       </c>
       <c r="O5" t="n">
-        <v>9.18</v>
+        <v>272</v>
       </c>
       <c r="P5" t="n">
-        <v>2.22</v>
+        <v>571.9300000000001</v>
       </c>
       <c r="Q5" t="n">
-        <v>55.26000000000001</v>
+        <v>100</v>
       </c>
       <c r="R5" t="n">
-        <v>243.87</v>
+        <v>81.87</v>
       </c>
       <c r="S5" t="n">
-        <v>82.33</v>
+        <v>100</v>
+      </c>
+      <c r="T5" t="n">
+        <v>103.01</v>
+      </c>
+      <c r="U5" t="n">
+        <v>12</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -3584,7 +3920,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ESG-Fx</t>
+          <t>EFG</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3593,22 +3929,22 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>212702.92</v>
+        <v>3546084</v>
       </c>
       <c r="E6" t="n">
-        <v>100</v>
+        <v>3402384.64</v>
       </c>
       <c r="F6" t="n">
-        <v>2664</v>
+        <v>16</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>907.6399999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>132249.57</v>
+        <v>2.9</v>
       </c>
       <c r="I6" t="n">
-        <v>18</v>
+        <v>8745.810000000001</v>
       </c>
       <c r="J6" t="n">
         <v>87850</v>
@@ -3617,28 +3953,37 @@
         <v>149694</v>
       </c>
       <c r="L6" t="n">
-        <v>68622</v>
+        <v>82522</v>
       </c>
       <c r="M6" t="n">
-        <v>397950</v>
+        <v>108882</v>
       </c>
       <c r="N6" t="n">
-        <v>14482.32</v>
+        <v>109090</v>
       </c>
       <c r="O6" t="n">
-        <v>401.72</v>
+        <v>541644</v>
       </c>
       <c r="P6" t="n">
-        <v>3.24</v>
+        <v>122928.56</v>
       </c>
       <c r="Q6" t="n">
-        <v>11609.88</v>
+        <v>98.31778903903904</v>
       </c>
       <c r="R6" t="n">
-        <v>27801.46</v>
+        <v>7975.959999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>25502.41</v>
+        <v>85.76730855855855</v>
+      </c>
+      <c r="T6" t="n">
+        <v>12963.51</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2664</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -3649,7 +3994,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ESG-Fx</t>
+          <t>EFG</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3658,22 +4003,22 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>57759.44</v>
+        <v>659659.42</v>
       </c>
       <c r="E7" t="n">
-        <v>100</v>
+        <v>599331.26</v>
       </c>
       <c r="F7" t="n">
-        <v>400</v>
+        <v>18.34</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>473.37</v>
       </c>
       <c r="H7" t="n">
-        <v>31370.22</v>
+        <v>2.69</v>
       </c>
       <c r="I7" t="n">
-        <v>19.74</v>
+        <v>3260.06</v>
       </c>
       <c r="J7" t="n">
         <v>12560</v>
@@ -3682,28 +4027,37 @@
         <v>15770</v>
       </c>
       <c r="L7" t="n">
-        <v>4611</v>
+        <v>11760</v>
       </c>
       <c r="M7" t="n">
-        <v>119710</v>
+        <v>14970</v>
       </c>
       <c r="N7" t="n">
-        <v>4768.59</v>
+        <v>19102</v>
       </c>
       <c r="O7" t="n">
-        <v>125.11</v>
+        <v>253983</v>
       </c>
       <c r="P7" t="n">
-        <v>3.03</v>
+        <v>47558.88</v>
       </c>
       <c r="Q7" t="n">
-        <v>2699.41</v>
+        <v>92.25575000000001</v>
       </c>
       <c r="R7" t="n">
-        <v>7451</v>
+        <v>9286.120000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>10925.75</v>
+        <v>92.56637500000001</v>
+      </c>
+      <c r="T7" t="n">
+        <v>9586.73</v>
+      </c>
+      <c r="U7" t="n">
+        <v>400</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -3714,7 +4068,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ESG-Fx</t>
+          <t>EFG</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3723,22 +4077,22 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>5355.04</v>
+        <v>21771.56</v>
       </c>
       <c r="E8" t="n">
-        <v>100</v>
+        <v>20185.07</v>
       </c>
       <c r="F8" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>19.8</v>
       </c>
       <c r="H8" t="n">
-        <v>3246.01</v>
+        <v>2.11</v>
       </c>
       <c r="I8" t="n">
-        <v>11</v>
+        <v>218.39</v>
       </c>
       <c r="J8" t="n">
         <v>315</v>
@@ -3747,28 +4101,37 @@
         <v>587</v>
       </c>
       <c r="L8" t="n">
-        <v>322</v>
+        <v>269</v>
       </c>
       <c r="M8" t="n">
-        <v>1561</v>
+        <v>366</v>
       </c>
       <c r="N8" t="n">
-        <v>494.94</v>
+        <v>237</v>
       </c>
       <c r="O8" t="n">
-        <v>22.89</v>
+        <v>704</v>
       </c>
       <c r="P8" t="n">
-        <v>2.34</v>
+        <v>1088.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>176.91</v>
+        <v>97.1182608695652</v>
       </c>
       <c r="R8" t="n">
-        <v>719.26</v>
+        <v>156.02</v>
       </c>
       <c r="S8" t="n">
-        <v>689.27</v>
+        <v>75.06913043478261</v>
+      </c>
+      <c r="T8" t="n">
+        <v>280.41</v>
+      </c>
+      <c r="U8" t="n">
+        <v>23</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -3779,7 +4142,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ESG-Fx</t>
+          <t>EFG</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3788,22 +4151,22 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1485963.2</v>
+        <v>1294199.46</v>
       </c>
       <c r="E9" t="n">
-        <v>100</v>
+        <v>861791.9299999999</v>
       </c>
       <c r="F9" t="n">
-        <v>400</v>
+        <v>43.66</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>361.57</v>
       </c>
       <c r="H9" t="n">
-        <v>1197479.47</v>
+        <v>3.07</v>
       </c>
       <c r="I9" t="n">
-        <v>260.17</v>
+        <v>10888.3</v>
       </c>
       <c r="J9" t="n">
         <v>73350</v>
@@ -3812,28 +4175,37 @@
         <v>210644</v>
       </c>
       <c r="L9" t="n">
-        <v>140363</v>
+        <v>72550</v>
       </c>
       <c r="M9" t="n">
-        <v>1241003</v>
+        <v>195587</v>
       </c>
       <c r="N9" t="n">
-        <v>24566.05</v>
+        <v>20131</v>
       </c>
       <c r="O9" t="n">
-        <v>466.14</v>
+        <v>91266</v>
       </c>
       <c r="P9" t="n">
-        <v>9.68</v>
+        <v>405481.66</v>
       </c>
       <c r="Q9" t="n">
-        <v>13175.53</v>
+        <v>16.259</v>
       </c>
       <c r="R9" t="n">
-        <v>150121.31</v>
+        <v>3832.62</v>
       </c>
       <c r="S9" t="n">
-        <v>100071.94</v>
+        <v>6.967750000000001</v>
+      </c>
+      <c r="T9" t="n">
+        <v>13723.8</v>
+      </c>
+      <c r="U9" t="n">
+        <v>400</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3847,103 +4219,142 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S9"/>
+  <dimension ref="A1:V9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="23" customWidth="1" min="15" max="15"/>
+    <col width="17" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="31" customWidth="1" min="18" max="18"/>
+    <col width="17" customWidth="1" min="19" max="19"/>
+    <col width="30" customWidth="1" min="20" max="20"/>
+    <col width="19" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>SPL Name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Approach</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Coverage Type</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Total Elapsed Time(ms)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Edge Coverage(%)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Processed Products</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Failed Products</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Test Generation Time(ms)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Test Generation Peak Memory(MB)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Number of ESGFx Vertices</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Number of ESGFx Edges</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Number of ESGFx Test Cases</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Number of ESGFx Test Events</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Test Case Recording Time(ms)</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Test Execution Time(ms)</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Test Execution Peak Memory(MB)</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>ESGFx Model Load Time(ms)</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Transformation Time(ms)</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Coverage Analysis Time(ms)</t>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>TotalElapsedTime(ms)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>GuitarGenTime(ms)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>TestGenPeakMemory(MB)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>TestExecTime(ms)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>TestExecPeakMemory(MB)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ESGFxModelLoadTime(ms)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>NumberOfESGFxVertices</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>NumberOfESGFxEdges</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>NumberOfEFGVertices</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>NumberOfEFGEdges</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>NumberOfEFGTestCases</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>NumberOfEFGTestEvents</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>ParsingTime(ms)</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>EventCoverage(%)</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>EventCoverageAnalysisTime(ms)</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>EdgeCoverage(%)</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>EdgeCoverageAnalysisTime(ms)</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>ProcessedProducts</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>FailedProducts</t>
         </is>
       </c>
     </row>
@@ -3955,7 +4366,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ESG-Fx</t>
+          <t>EFG</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3964,22 +4375,22 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>37515.96</v>
+        <v>707441.1899999999</v>
       </c>
       <c r="E2" t="n">
-        <v>91.59991967871487</v>
+        <v>667225.2100000001</v>
       </c>
       <c r="F2" t="n">
-        <v>498</v>
+        <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>192.11</v>
       </c>
       <c r="H2" t="n">
-        <v>20962.98</v>
+        <v>2.59</v>
       </c>
       <c r="I2" t="n">
-        <v>11</v>
+        <v>3380.58</v>
       </c>
       <c r="J2" t="n">
         <v>12660</v>
@@ -3988,28 +4399,37 @@
         <v>16395</v>
       </c>
       <c r="L2" t="n">
-        <v>4218</v>
+        <v>11664</v>
       </c>
       <c r="M2" t="n">
-        <v>9492</v>
+        <v>9939</v>
       </c>
       <c r="N2" t="n">
-        <v>2658.76</v>
+        <v>5883</v>
       </c>
       <c r="O2" t="n">
-        <v>101.38</v>
+        <v>22374</v>
       </c>
       <c r="P2" t="n">
-        <v>2.71</v>
+        <v>33897.28</v>
       </c>
       <c r="Q2" t="n">
-        <v>2907.9</v>
+        <v>100</v>
       </c>
       <c r="R2" t="n">
-        <v>7461.85</v>
+        <v>1928.3</v>
       </c>
       <c r="S2" t="n">
-        <v>3352.56</v>
+        <v>98.80202811244979</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2918.01</v>
+      </c>
+      <c r="U2" t="n">
+        <v>498</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -4020,7 +4440,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ESG-Fx</t>
+          <t>EFG</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -4029,22 +4449,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>24908.86</v>
+        <v>50268.67</v>
       </c>
       <c r="E3" t="n">
-        <v>100</v>
+        <v>42370.22</v>
       </c>
       <c r="F3" t="n">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>16974.32</v>
+        <v>2.16</v>
       </c>
       <c r="I3" t="n">
-        <v>31.86</v>
+        <v>469.75</v>
       </c>
       <c r="J3" t="n">
         <v>554</v>
@@ -4053,28 +4473,37 @@
         <v>1566</v>
       </c>
       <c r="L3" t="n">
-        <v>3360</v>
+        <v>470</v>
       </c>
       <c r="M3" t="n">
-        <v>5854</v>
+        <v>1144</v>
       </c>
       <c r="N3" t="n">
-        <v>1317.58</v>
+        <v>2768</v>
       </c>
       <c r="O3" t="n">
-        <v>39.24</v>
+        <v>11218</v>
       </c>
       <c r="P3" t="n">
-        <v>2.89</v>
+        <v>5794.99</v>
       </c>
       <c r="Q3" t="n">
-        <v>491.84</v>
+        <v>100</v>
       </c>
       <c r="R3" t="n">
-        <v>3142.92</v>
+        <v>1472.9</v>
       </c>
       <c r="S3" t="n">
-        <v>2790</v>
+        <v>100</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1482.2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>42</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -4085,7 +4514,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ESG-Fx</t>
+          <t>EFG</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -4094,22 +4523,22 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>95316.54999999999</v>
+        <v>793675.9099999999</v>
       </c>
       <c r="E4" t="n">
-        <v>100</v>
+        <v>709146.3</v>
       </c>
       <c r="F4" t="n">
-        <v>416</v>
+        <v>18</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>500.49</v>
       </c>
       <c r="H4" t="n">
-        <v>50196.64999999999</v>
+        <v>2.95</v>
       </c>
       <c r="I4" t="n">
-        <v>20.94</v>
+        <v>5025.57</v>
       </c>
       <c r="J4" t="n">
         <v>25817</v>
@@ -4118,28 +4547,37 @@
         <v>29727</v>
       </c>
       <c r="L4" t="n">
-        <v>4618</v>
+        <v>24985</v>
       </c>
       <c r="M4" t="n">
-        <v>218547</v>
+        <v>28895</v>
       </c>
       <c r="N4" t="n">
-        <v>7070.93</v>
+        <v>19134</v>
       </c>
       <c r="O4" t="n">
-        <v>201.17</v>
+        <v>248570</v>
       </c>
       <c r="P4" t="n">
-        <v>3.25</v>
+        <v>68705.71000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>3911.2</v>
+        <v>39.00603365384615</v>
       </c>
       <c r="R4" t="n">
-        <v>17348.23</v>
+        <v>5403.93</v>
       </c>
       <c r="S4" t="n">
-        <v>16492.24</v>
+        <v>40.29302884615385</v>
+      </c>
+      <c r="T4" t="n">
+        <v>9143.610000000001</v>
+      </c>
+      <c r="U4" t="n">
+        <v>416</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -4150,7 +4588,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ESG-Fx</t>
+          <t>EFG</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4159,22 +4597,22 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1878.87</v>
+        <v>11911.92</v>
       </c>
       <c r="E5" t="n">
-        <v>100</v>
+        <v>11171.19</v>
       </c>
       <c r="F5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>10.33</v>
       </c>
       <c r="H5" t="n">
-        <v>1097.85</v>
+        <v>2.1</v>
       </c>
       <c r="I5" t="n">
-        <v>9</v>
+        <v>60.77</v>
       </c>
       <c r="J5" t="n">
         <v>110</v>
@@ -4183,28 +4621,37 @@
         <v>108</v>
       </c>
       <c r="L5" t="n">
-        <v>22</v>
+        <v>86</v>
       </c>
       <c r="M5" t="n">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="N5" t="n">
-        <v>334.12</v>
+        <v>46</v>
       </c>
       <c r="O5" t="n">
-        <v>9.56</v>
+        <v>229</v>
       </c>
       <c r="P5" t="n">
-        <v>2.22</v>
+        <v>538.45</v>
       </c>
       <c r="Q5" t="n">
-        <v>48.81</v>
+        <v>100</v>
       </c>
       <c r="R5" t="n">
-        <v>264.31</v>
+        <v>65.03</v>
       </c>
       <c r="S5" t="n">
-        <v>87.83</v>
+        <v>100</v>
+      </c>
+      <c r="T5" t="n">
+        <v>87.57000000000001</v>
+      </c>
+      <c r="U5" t="n">
+        <v>12</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -4215,7 +4662,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ESG-Fx</t>
+          <t>EFG</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4224,22 +4671,22 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>401939.41</v>
+        <v>3716421.42</v>
       </c>
       <c r="E6" t="n">
-        <v>100</v>
+        <v>3542691.54</v>
       </c>
       <c r="F6" t="n">
-        <v>2664</v>
+        <v>17</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1047.91</v>
       </c>
       <c r="H6" t="n">
-        <v>253821.64</v>
+        <v>2.91</v>
       </c>
       <c r="I6" t="n">
-        <v>24</v>
+        <v>8523.639999999999</v>
       </c>
       <c r="J6" t="n">
         <v>87850</v>
@@ -4248,28 +4695,37 @@
         <v>149694</v>
       </c>
       <c r="L6" t="n">
-        <v>117192</v>
+        <v>82522</v>
       </c>
       <c r="M6" t="n">
-        <v>654272</v>
+        <v>108882</v>
       </c>
       <c r="N6" t="n">
-        <v>25551.98</v>
+        <v>132636</v>
       </c>
       <c r="O6" t="n">
-        <v>449.65</v>
+        <v>740822</v>
       </c>
       <c r="P6" t="n">
-        <v>3.55</v>
+        <v>145523.36</v>
       </c>
       <c r="Q6" t="n">
-        <v>13390.8</v>
+        <v>100</v>
       </c>
       <c r="R6" t="n">
-        <v>55530.78</v>
+        <v>9718.25</v>
       </c>
       <c r="S6" t="n">
-        <v>51217.07</v>
+        <v>86.93719219219219</v>
+      </c>
+      <c r="T6" t="n">
+        <v>15281.73</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2664</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -4280,7 +4736,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ESG-Fx</t>
+          <t>EFG</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4289,22 +4745,22 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>75923.48</v>
+        <v>687461.8600000001</v>
       </c>
       <c r="E7" t="n">
-        <v>100</v>
+        <v>614102.8999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>400</v>
+        <v>28.36</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>528.71</v>
       </c>
       <c r="H7" t="n">
-        <v>40081.91</v>
+        <v>2.73</v>
       </c>
       <c r="I7" t="n">
-        <v>38.25</v>
+        <v>3200.75</v>
       </c>
       <c r="J7" t="n">
         <v>12560</v>
@@ -4313,28 +4769,37 @@
         <v>15770</v>
       </c>
       <c r="L7" t="n">
-        <v>5673</v>
+        <v>11760</v>
       </c>
       <c r="M7" t="n">
-        <v>143125</v>
+        <v>14970</v>
       </c>
       <c r="N7" t="n">
-        <v>6123.309999999999</v>
+        <v>24682</v>
       </c>
       <c r="O7" t="n">
-        <v>125.39</v>
+        <v>338669</v>
       </c>
       <c r="P7" t="n">
-        <v>3.56</v>
+        <v>58138.72</v>
       </c>
       <c r="Q7" t="n">
-        <v>2917.71</v>
+        <v>92.25575000000001</v>
       </c>
       <c r="R7" t="n">
-        <v>11276.21</v>
+        <v>10952.68</v>
       </c>
       <c r="S7" t="n">
-        <v>15318.95</v>
+        <v>92.56637500000001</v>
+      </c>
+      <c r="T7" t="n">
+        <v>11115.1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>400</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -4345,7 +4810,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ESG-Fx</t>
+          <t>EFG</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4354,22 +4819,22 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10641.26</v>
+        <v>23364.71</v>
       </c>
       <c r="E8" t="n">
-        <v>96.47739130434783</v>
+        <v>21421.51</v>
       </c>
       <c r="F8" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>24.41</v>
       </c>
       <c r="H8" t="n">
-        <v>6413.43</v>
+        <v>2.12</v>
       </c>
       <c r="I8" t="n">
-        <v>15</v>
+        <v>192.1</v>
       </c>
       <c r="J8" t="n">
         <v>315</v>
@@ -4378,28 +4843,37 @@
         <v>587</v>
       </c>
       <c r="L8" t="n">
-        <v>793</v>
+        <v>269</v>
       </c>
       <c r="M8" t="n">
-        <v>4031</v>
+        <v>366</v>
       </c>
       <c r="N8" t="n">
-        <v>666.49</v>
+        <v>408</v>
       </c>
       <c r="O8" t="n">
-        <v>23.27</v>
+        <v>1567</v>
       </c>
       <c r="P8" t="n">
-        <v>2.55</v>
+        <v>1480.96</v>
       </c>
       <c r="Q8" t="n">
-        <v>224.68</v>
+        <v>100</v>
       </c>
       <c r="R8" t="n">
-        <v>1455.27</v>
+        <v>253.46</v>
       </c>
       <c r="S8" t="n">
-        <v>1780.64</v>
+        <v>82.08086956521738</v>
+      </c>
+      <c r="T8" t="n">
+        <v>423.76</v>
+      </c>
+      <c r="U8" t="n">
+        <v>23</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -4410,7 +4884,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ESG-Fx</t>
+          <t>EFG</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4419,22 +4893,22 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2471757.77</v>
+        <v>1403184.85</v>
       </c>
       <c r="E9" t="n">
-        <v>100</v>
+        <v>923838.34</v>
       </c>
       <c r="F9" t="n">
-        <v>400</v>
+        <v>50.69</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>598.29</v>
       </c>
       <c r="H9" t="n">
-        <v>2022030.65</v>
+        <v>3.09</v>
       </c>
       <c r="I9" t="n">
-        <v>454.09</v>
+        <v>11039.57</v>
       </c>
       <c r="J9" t="n">
         <v>73350</v>
@@ -4443,28 +4917,37 @@
         <v>210644</v>
       </c>
       <c r="L9" t="n">
-        <v>193641</v>
+        <v>72550</v>
       </c>
       <c r="M9" t="n">
-        <v>1606648</v>
+        <v>195587</v>
       </c>
       <c r="N9" t="n">
-        <v>25841.35</v>
+        <v>43556</v>
       </c>
       <c r="O9" t="n">
-        <v>376.52</v>
+        <v>240836</v>
       </c>
       <c r="P9" t="n">
-        <v>23.03</v>
+        <v>451260.28</v>
       </c>
       <c r="Q9" t="n">
-        <v>11744.82</v>
+        <v>20.14675</v>
       </c>
       <c r="R9" t="n">
-        <v>283572.01</v>
+        <v>6581.9</v>
       </c>
       <c r="S9" t="n">
-        <v>126036.15</v>
+        <v>10.455875</v>
+      </c>
+      <c r="T9" t="n">
+        <v>18629.5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>400</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4478,133 +4961,166 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y9"/>
+  <dimension ref="A1:Z9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="27" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="25" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="31" customWidth="1" min="17" max="17"/>
+    <col width="17" customWidth="1" min="18" max="18"/>
+    <col width="30" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="21" customWidth="1" min="21" max="21"/>
+    <col width="26" customWidth="1" min="22" max="22"/>
+    <col width="23" customWidth="1" min="23" max="23"/>
+    <col width="33" customWidth="1" min="24" max="24"/>
+    <col width="19" customWidth="1" min="25" max="25"/>
+    <col width="16" customWidth="1" min="26" max="26"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>SPL Name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Approach</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Coverage Type</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Total Elapsed Time(ms)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Event Coverage(%)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Edge Coverage(%)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Processed Products</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Failed Products</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Model Load Time(ms)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Test Gen Time(ms)</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Test Gen Peak Memory(MB)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Total Vertices</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Total Edges</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Total Test Cases</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Total Test Events</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Aborted Sequences</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>TestCase Recording Time(ms)</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Event Coverage Analysis  Time(ms)</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Edge Coverage Analysis  Time(ms)</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Test Exec Time(ms)</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Test Exec Peak Memory(MB)</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Safety Limit Hit Count</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Avg Time on Safety Limit(ms)</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Avg Steps on Safety Limit</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Avg Edge Coverage on Safety Limit(%)</t>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>TotalElapsedTime(ms)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>TotalTestGenTime(ms)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>AlgTestGenTime(ms)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ESGFxModelLoadTime(ms)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>TestCaseRecordingTime(ms)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>TestGenPeakMemory(MB)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>TestExecTime(ms)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>TestExecPeakMemory(MB)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>NumberOfESGFxVertices</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>NumberOfESGFxEdges</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>NumberOfESGFxTestCases</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>NumberOfESGFxTestEvents</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>EventCoverage(%)</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>EventCoverageAnalysisTime(ms)</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>EdgeCoverage(%)</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>EdgeCoverageAnalysisTime(ms)</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>AbortedSequences</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>SafetyLimitHitCount</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>AvgTimeOnSafetyLimit(ms)</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>AvgStepsOnSafetyLimit</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>AvgEdgeCoverageOnSafetyLimit(%)</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>ProcessedProducts</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>FailedProducts</t>
         </is>
       </c>
     </row>
@@ -4625,28 +5141,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15150.22</v>
+        <v>17154.2</v>
       </c>
       <c r="E2" t="n">
-        <v>100</v>
+        <v>12964.07</v>
       </c>
       <c r="F2" t="n">
-        <v>100</v>
+        <v>6230.46</v>
       </c>
       <c r="G2" t="n">
-        <v>498</v>
+        <v>3350.79</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>3382.82</v>
       </c>
       <c r="I2" t="n">
-        <v>2843.06</v>
+        <v>12.14</v>
       </c>
       <c r="J2" t="n">
-        <v>5495.66</v>
+        <v>131.92</v>
       </c>
       <c r="K2" t="n">
-        <v>12.14</v>
+        <v>2.63</v>
       </c>
       <c r="L2" t="n">
         <v>12660</v>
@@ -4661,29 +5177,32 @@
         <v>18181</v>
       </c>
       <c r="P2" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1508.6</v>
+      </c>
+      <c r="R2" t="n">
+        <v>100</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2603.8</v>
+      </c>
+      <c r="T2" t="n">
         <v>68326</v>
       </c>
-      <c r="Q2" t="n">
-        <v>2919.16</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1472.59</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2318.2</v>
-      </c>
-      <c r="T2" t="n">
-        <v>123.87</v>
-      </c>
       <c r="U2" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
+      <c r="Y2" t="n">
+        <v>498</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4702,28 +5221,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3997.530000000001</v>
+        <v>4363.150000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>100</v>
+        <v>2329.91</v>
       </c>
       <c r="F3" t="n">
-        <v>100</v>
+        <v>815.08</v>
       </c>
       <c r="G3" t="n">
-        <v>42</v>
+        <v>439.48</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1075.35</v>
       </c>
       <c r="I3" t="n">
-        <v>355.89</v>
+        <v>7</v>
       </c>
       <c r="J3" t="n">
-        <v>705.02</v>
+        <v>53.37</v>
       </c>
       <c r="K3" t="n">
-        <v>7</v>
+        <v>2.1</v>
       </c>
       <c r="L3" t="n">
         <v>554</v>
@@ -4738,29 +5257,32 @@
         <v>6833</v>
       </c>
       <c r="P3" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>915.62</v>
+      </c>
+      <c r="R3" t="n">
+        <v>100</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1172.82</v>
+      </c>
+      <c r="T3" t="n">
         <v>3358</v>
       </c>
-      <c r="Q3" t="n">
-        <v>1005.85</v>
-      </c>
-      <c r="R3" t="n">
-        <v>816.3499999999999</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1062.02</v>
-      </c>
-      <c r="T3" t="n">
-        <v>47.25</v>
-      </c>
       <c r="U3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
+      <c r="Y3" t="n">
+        <v>42</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4779,28 +5301,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>382416.65</v>
+        <v>400128.9</v>
       </c>
       <c r="E4" t="n">
-        <v>97.15168269230769</v>
+        <v>382984.89</v>
       </c>
       <c r="F4" t="n">
-        <v>96.10319711538462</v>
+        <v>370565.08</v>
       </c>
       <c r="G4" t="n">
-        <v>416</v>
+        <v>4798.46</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>7621.349999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>4769.93</v>
+        <v>135.52</v>
       </c>
       <c r="J4" t="n">
-        <v>354365.48</v>
+        <v>487.4299999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>135.52</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
         <v>25817</v>
@@ -4815,34 +5337,37 @@
         <v>319870</v>
       </c>
       <c r="P4" t="n">
+        <v>97.15168269230769</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>6831.46</v>
+      </c>
+      <c r="R4" t="n">
+        <v>96.10319711538462</v>
+      </c>
+      <c r="S4" t="n">
+        <v>8939.860000000001</v>
+      </c>
+      <c r="T4" t="n">
         <v>70472564</v>
       </c>
-      <c r="Q4" t="n">
-        <v>7660.19</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6702.84</v>
-      </c>
-      <c r="S4" t="n">
-        <v>8845.689999999999</v>
-      </c>
-      <c r="T4" t="n">
-        <v>515.59</v>
-      </c>
       <c r="U4" t="n">
-        <v>2.99</v>
+        <v>349</v>
       </c>
       <c r="V4" t="n">
-        <v>349</v>
+        <v>926.3265042979941</v>
       </c>
       <c r="W4" t="n">
-        <v>893.1546704871059</v>
+        <v>1198807.192034384</v>
       </c>
       <c r="X4" t="n">
-        <v>1198807.192034384</v>
+        <v>95.48561604584526</v>
       </c>
       <c r="Y4" t="n">
-        <v>95.48561604584526</v>
+        <v>416</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -4862,28 +5387,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>660.85</v>
+        <v>763.8399999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>100</v>
+        <v>638.1800000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>100</v>
+        <v>112.28</v>
       </c>
       <c r="G5" t="n">
-        <v>12</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>460.47</v>
       </c>
       <c r="I5" t="n">
-        <v>49.17</v>
+        <v>6</v>
       </c>
       <c r="J5" t="n">
-        <v>100.07</v>
+        <v>10.99</v>
       </c>
       <c r="K5" t="n">
-        <v>6</v>
+        <v>2.01</v>
       </c>
       <c r="L5" t="n">
         <v>110</v>
@@ -4898,29 +5423,32 @@
         <v>109</v>
       </c>
       <c r="P5" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>48.13</v>
+      </c>
+      <c r="R5" t="n">
+        <v>100</v>
+      </c>
+      <c r="S5" t="n">
+        <v>65.06999999999999</v>
+      </c>
+      <c r="T5" t="n">
         <v>54</v>
       </c>
-      <c r="Q5" t="n">
-        <v>382.34</v>
-      </c>
-      <c r="R5" t="n">
-        <v>46.09</v>
-      </c>
-      <c r="S5" t="n">
-        <v>59.75</v>
-      </c>
-      <c r="T5" t="n">
-        <v>9.18</v>
-      </c>
       <c r="U5" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
+      <c r="Y5" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4939,28 +5467,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>121538.6</v>
+        <v>135040.71</v>
       </c>
       <c r="E6" t="n">
-        <v>100</v>
+        <v>98672.66999999998</v>
       </c>
       <c r="F6" t="n">
-        <v>100</v>
+        <v>64660.39</v>
       </c>
       <c r="G6" t="n">
-        <v>2664</v>
+        <v>13703.54</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>20308.74</v>
       </c>
       <c r="I6" t="n">
-        <v>12500.49</v>
+        <v>19.45</v>
       </c>
       <c r="J6" t="n">
-        <v>58690.67999999999</v>
+        <v>916.47</v>
       </c>
       <c r="K6" t="n">
-        <v>19.44</v>
+        <v>2.95</v>
       </c>
       <c r="L6" t="n">
         <v>87850</v>
@@ -4975,29 +5503,32 @@
         <v>671484</v>
       </c>
       <c r="P6" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>12777.46</v>
+      </c>
+      <c r="R6" t="n">
+        <v>100</v>
+      </c>
+      <c r="S6" t="n">
+        <v>23954.54</v>
+      </c>
+      <c r="T6" t="n">
         <v>2238118</v>
       </c>
-      <c r="Q6" t="n">
-        <v>16823.65</v>
-      </c>
-      <c r="R6" t="n">
-        <v>11621.15</v>
-      </c>
-      <c r="S6" t="n">
-        <v>21379.63</v>
-      </c>
-      <c r="T6" t="n">
-        <v>865.1099999999999</v>
-      </c>
       <c r="U6" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
+      <c r="Y6" t="n">
+        <v>2664</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5016,28 +5547,28 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>42970.38</v>
+        <v>46875.92</v>
       </c>
       <c r="E7" t="n">
-        <v>96.590625</v>
+        <v>33083.66</v>
       </c>
       <c r="F7" t="n">
-        <v>99.99600000000001</v>
+        <v>23370.56</v>
       </c>
       <c r="G7" t="n">
-        <v>400</v>
+        <v>3381.87</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>6331.23</v>
       </c>
       <c r="I7" t="n">
-        <v>2923.67</v>
+        <v>33.26</v>
       </c>
       <c r="J7" t="n">
-        <v>21281.26</v>
+        <v>341.83</v>
       </c>
       <c r="K7" t="n">
-        <v>33.26</v>
+        <v>2.72</v>
       </c>
       <c r="L7" t="n">
         <v>12560</v>
@@ -5052,34 +5583,37 @@
         <v>177958</v>
       </c>
       <c r="P7" t="n">
+        <v>96.590625</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>6575.02</v>
+      </c>
+      <c r="R7" t="n">
+        <v>99.99600000000001</v>
+      </c>
+      <c r="S7" t="n">
+        <v>7282.210000000001</v>
+      </c>
+      <c r="T7" t="n">
         <v>1491138</v>
       </c>
-      <c r="Q7" t="n">
-        <v>5509.27</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6042.609999999999</v>
-      </c>
-      <c r="S7" t="n">
-        <v>6567</v>
-      </c>
-      <c r="T7" t="n">
-        <v>327.79</v>
-      </c>
       <c r="U7" t="n">
-        <v>2.72</v>
+        <v>1</v>
       </c>
       <c r="V7" t="n">
-        <v>1</v>
+        <v>436</v>
       </c>
       <c r="W7" t="n">
-        <v>413</v>
+        <v>233280</v>
       </c>
       <c r="X7" t="n">
-        <v>233280</v>
+        <v>98.45999999999999</v>
       </c>
       <c r="Y7" t="n">
-        <v>98.45999999999999</v>
+        <v>400</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -5099,28 +5633,28 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1877.35</v>
+        <v>2118.07</v>
       </c>
       <c r="E8" t="n">
-        <v>100</v>
+        <v>1330.67</v>
       </c>
       <c r="F8" t="n">
-        <v>100</v>
+        <v>528.33</v>
       </c>
       <c r="G8" t="n">
-        <v>23</v>
+        <v>209.89</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>592.45</v>
       </c>
       <c r="I8" t="n">
-        <v>187.61</v>
+        <v>7</v>
       </c>
       <c r="J8" t="n">
-        <v>447.48</v>
+        <v>24.13</v>
       </c>
       <c r="K8" t="n">
-        <v>7</v>
+        <v>2.07</v>
       </c>
       <c r="L8" t="n">
         <v>315</v>
@@ -5135,29 +5669,32 @@
         <v>1827</v>
       </c>
       <c r="P8" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>310.86</v>
+      </c>
+      <c r="R8" t="n">
+        <v>100</v>
+      </c>
+      <c r="S8" t="n">
+        <v>490.67</v>
+      </c>
+      <c r="T8" t="n">
         <v>1945</v>
       </c>
-      <c r="Q8" t="n">
-        <v>525.1900000000001</v>
-      </c>
-      <c r="R8" t="n">
-        <v>277.39</v>
-      </c>
-      <c r="S8" t="n">
-        <v>435.94</v>
-      </c>
-      <c r="T8" t="n">
-        <v>24.27</v>
-      </c>
       <c r="U8" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
+      <c r="Y8" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5176,28 +5713,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1781791.81</v>
+        <v>1918260.97</v>
       </c>
       <c r="E9" t="n">
-        <v>95.59362499999999</v>
+        <v>730936.54</v>
       </c>
       <c r="F9" t="n">
-        <v>84.72325000000001</v>
+        <v>631847.8200000001</v>
       </c>
       <c r="G9" t="n">
-        <v>400</v>
+        <v>10013.21</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>89075.51000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>9264.67</v>
+        <v>311.59</v>
       </c>
       <c r="J9" t="n">
-        <v>588090.29</v>
+        <v>9583.959999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>311.58</v>
+        <v>10.84</v>
       </c>
       <c r="L9" t="n">
         <v>73350</v>
@@ -5212,34 +5749,37 @@
         <v>36851871</v>
       </c>
       <c r="P9" t="n">
+        <v>95.59362499999999</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>195980.68</v>
+      </c>
+      <c r="R9" t="n">
+        <v>84.72325000000001</v>
+      </c>
+      <c r="S9" t="n">
+        <v>977624.8100000001</v>
+      </c>
+      <c r="T9" t="n">
         <v>116424084</v>
       </c>
-      <c r="Q9" t="n">
-        <v>83702.11</v>
-      </c>
-      <c r="R9" t="n">
-        <v>185247.69</v>
-      </c>
-      <c r="S9" t="n">
-        <v>903612.4</v>
-      </c>
-      <c r="T9" t="n">
-        <v>9019.51</v>
-      </c>
       <c r="U9" t="n">
-        <v>11.27</v>
+        <v>400</v>
       </c>
       <c r="V9" t="n">
+        <v>1574.4575</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="X9" t="n">
+        <v>85.47437499999999</v>
+      </c>
+      <c r="Y9" t="n">
         <v>400</v>
       </c>
-      <c r="W9" t="n">
-        <v>1464.91</v>
-      </c>
-      <c r="X9" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>85.47437499999999</v>
+      <c r="Z9" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
